--- a/database/event/8301/event_8301_evp_summary.xlsx
+++ b/database/event/8301/event_8301_evp_summary.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="EVP_Summary_8301" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Per_Map_Scores" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EVP_Summary_8301" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Per_Map_Scores" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -502,7 +502,7 @@
         <v>5.8935</v>
       </c>
       <c r="D2" t="n">
-        <v>3.163</v>
+        <v>3.5611</v>
       </c>
       <c r="E2" t="n">
         <v>9.8582</v>
@@ -548,7 +548,7 @@
         <v>5.4851</v>
       </c>
       <c r="D3" t="n">
-        <v>2.9103</v>
+        <v>3.2852</v>
       </c>
       <c r="E3" t="n">
         <v>9.1751</v>
@@ -594,7 +594,7 @@
         <v>4.6915</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4191</v>
+        <v>2.7489</v>
       </c>
       <c r="E4" t="n">
         <v>7.8476</v>
@@ -640,7 +640,7 @@
         <v>4.259</v>
       </c>
       <c r="D5" t="n">
-        <v>2.1514</v>
+        <v>2.4566</v>
       </c>
       <c r="E5" t="n">
         <v>7.1241</v>
@@ -686,7 +686,7 @@
         <v>4.0461</v>
       </c>
       <c r="D6" t="n">
-        <v>2.0197</v>
+        <v>2.3128</v>
       </c>
       <c r="E6" t="n">
         <v>6.768</v>
@@ -732,7 +732,7 @@
         <v>4.0439</v>
       </c>
       <c r="D7" t="n">
-        <v>2.0183</v>
+        <v>2.3113</v>
       </c>
       <c r="E7" t="n">
         <v>6.7644</v>
@@ -778,7 +778,7 @@
         <v>3.9337</v>
       </c>
       <c r="D8" t="n">
-        <v>1.9501</v>
+        <v>2.2368</v>
       </c>
       <c r="E8" t="n">
         <v>6.58</v>
@@ -824,7 +824,7 @@
         <v>3.8804</v>
       </c>
       <c r="D9" t="n">
-        <v>1.9171</v>
+        <v>2.2008</v>
       </c>
       <c r="E9" t="n">
         <v>6.4908</v>
@@ -870,7 +870,7 @@
         <v>3.7882</v>
       </c>
       <c r="D10" t="n">
-        <v>1.86</v>
+        <v>2.1385</v>
       </c>
       <c r="E10" t="n">
         <v>6.3366</v>
@@ -916,7 +916,7 @@
         <v>3.7523</v>
       </c>
       <c r="D11" t="n">
-        <v>1.8378</v>
+        <v>2.1142</v>
       </c>
       <c r="E11" t="n">
         <v>6.2765</v>
@@ -962,7 +962,7 @@
         <v>3.6013</v>
       </c>
       <c r="D12" t="n">
-        <v>1.7443</v>
+        <v>2.0122</v>
       </c>
       <c r="E12" t="n">
         <v>6.0239</v>
@@ -1008,7 +1008,7 @@
         <v>2.9321</v>
       </c>
       <c r="D13" t="n">
-        <v>1.3302</v>
+        <v>1.56</v>
       </c>
       <c r="E13" t="n">
         <v>4.9046</v>
@@ -1054,7 +1054,7 @@
         <v>2.7815</v>
       </c>
       <c r="D14" t="n">
-        <v>1.237</v>
+        <v>1.4582</v>
       </c>
       <c r="E14" t="n">
         <v>4.6526</v>
@@ -1100,7 +1100,7 @@
         <v>2.6421</v>
       </c>
       <c r="D15" t="n">
-        <v>1.1507</v>
+        <v>1.364</v>
       </c>
       <c r="E15" t="n">
         <v>4.4195</v>
@@ -1146,7 +1146,7 @@
         <v>2.0743</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7993</v>
+        <v>0.9802999999999999</v>
       </c>
       <c r="E16" t="n">
         <v>3.4697</v>
@@ -1192,7 +1192,7 @@
         <v>2.0158</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7631</v>
+        <v>0.9408</v>
       </c>
       <c r="E17" t="n">
         <v>3.3718</v>
@@ -1238,7 +1238,7 @@
         <v>1.9958</v>
       </c>
       <c r="D18" t="n">
-        <v>0.7507</v>
+        <v>0.9273</v>
       </c>
       <c r="E18" t="n">
         <v>3.3384</v>
@@ -1284,7 +1284,7 @@
         <v>1.8563</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6643</v>
+        <v>0.833</v>
       </c>
       <c r="E19" t="n">
         <v>3.105</v>
@@ -1330,7 +1330,7 @@
         <v>1.6318</v>
       </c>
       <c r="D20" t="n">
-        <v>0.5254</v>
+        <v>0.6813</v>
       </c>
       <c r="E20" t="n">
         <v>2.7295</v>
@@ -1376,7 +1376,7 @@
         <v>1.6138</v>
       </c>
       <c r="D21" t="n">
-        <v>0.5143</v>
+        <v>0.6691</v>
       </c>
       <c r="E21" t="n">
         <v>2.6994</v>
@@ -1422,7 +1422,7 @@
         <v>1.5689</v>
       </c>
       <c r="D22" t="n">
-        <v>0.4865</v>
+        <v>0.6388</v>
       </c>
       <c r="E22" t="n">
         <v>2.6243</v>
@@ -1468,7 +1468,7 @@
         <v>1.5482</v>
       </c>
       <c r="D23" t="n">
-        <v>0.4737</v>
+        <v>0.6248</v>
       </c>
       <c r="E23" t="n">
         <v>2.5897</v>
@@ -1514,7 +1514,7 @@
         <v>1.5194</v>
       </c>
       <c r="D24" t="n">
-        <v>0.4558</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="E24" t="n">
         <v>2.5415</v>
@@ -1560,7 +1560,7 @@
         <v>1.5123</v>
       </c>
       <c r="D25" t="n">
-        <v>0.4514</v>
+        <v>0.6005</v>
       </c>
       <c r="E25" t="n">
         <v>2.5296</v>
@@ -1606,7 +1606,7 @@
         <v>1.4991</v>
       </c>
       <c r="D26" t="n">
-        <v>0.4433</v>
+        <v>0.5917</v>
       </c>
       <c r="E26" t="n">
         <v>2.5076</v>
@@ -1652,7 +1652,7 @@
         <v>1.4287</v>
       </c>
       <c r="D27" t="n">
-        <v>0.3997</v>
+        <v>0.5441</v>
       </c>
       <c r="E27" t="n">
         <v>2.3899</v>
@@ -1698,7 +1698,7 @@
         <v>1.3717</v>
       </c>
       <c r="D28" t="n">
-        <v>0.3644</v>
+        <v>0.5054999999999999</v>
       </c>
       <c r="E28" t="n">
         <v>2.2944</v>
@@ -1744,7 +1744,7 @@
         <v>1.3564</v>
       </c>
       <c r="D29" t="n">
-        <v>0.3549</v>
+        <v>0.4952</v>
       </c>
       <c r="E29" t="n">
         <v>2.2688</v>
@@ -1790,7 +1790,7 @@
         <v>1.1341</v>
       </c>
       <c r="D30" t="n">
-        <v>0.2174</v>
+        <v>0.345</v>
       </c>
       <c r="E30" t="n">
         <v>1.897</v>
@@ -1836,7 +1836,7 @@
         <v>1.0438</v>
       </c>
       <c r="D31" t="n">
-        <v>0.1615</v>
+        <v>0.284</v>
       </c>
       <c r="E31" t="n">
         <v>1.746</v>
@@ -1882,7 +1882,7 @@
         <v>0.9875</v>
       </c>
       <c r="D32" t="n">
-        <v>0.1267</v>
+        <v>0.2459</v>
       </c>
       <c r="E32" t="n">
         <v>1.6518</v>
@@ -1928,7 +1928,7 @@
         <v>0.9127999999999999</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0804</v>
+        <v>0.1954</v>
       </c>
       <c r="E33" t="n">
         <v>1.5268</v>
@@ -1974,7 +1974,7 @@
         <v>0.9025</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0741</v>
+        <v>0.1885</v>
       </c>
       <c r="E34" t="n">
         <v>1.5097</v>
@@ -2020,7 +2020,7 @@
         <v>0.8018999999999999</v>
       </c>
       <c r="D35" t="n">
-        <v>0.0118</v>
+        <v>0.1205</v>
       </c>
       <c r="E35" t="n">
         <v>1.3413</v>
@@ -2066,7 +2066,7 @@
         <v>0.7796999999999999</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.0019</v>
+        <v>0.1055</v>
       </c>
       <c r="E36" t="n">
         <v>1.3043</v>
@@ -2112,7 +2112,7 @@
         <v>0.6886</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.0583</v>
+        <v>0.044</v>
       </c>
       <c r="E37" t="n">
         <v>1.1519</v>
@@ -2158,7 +2158,7 @@
         <v>0.6596</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.07630000000000001</v>
+        <v>0.0243</v>
       </c>
       <c r="E38" t="n">
         <v>1.1033</v>
@@ -2204,7 +2204,7 @@
         <v>0.6238</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.0985</v>
+        <v>0.0001</v>
       </c>
       <c r="E39" t="n">
         <v>1.0434</v>
@@ -2250,7 +2250,7 @@
         <v>0.6176</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.1023</v>
+        <v>-0.004</v>
       </c>
       <c r="E40" t="n">
         <v>1.0331</v>
@@ -2296,7 +2296,7 @@
         <v>0.5635</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.1358</v>
+        <v>-0.0406</v>
       </c>
       <c r="E41" t="n">
         <v>0.9425</v>
@@ -2342,7 +2342,7 @@
         <v>0.5403</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.1501</v>
+        <v>-0.0563</v>
       </c>
       <c r="E42" t="n">
         <v>0.9036999999999999</v>
@@ -2388,7 +2388,7 @@
         <v>0.4607</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.1994</v>
+        <v>-0.11</v>
       </c>
       <c r="E43" t="n">
         <v>0.7707000000000001</v>
@@ -2434,7 +2434,7 @@
         <v>0.4178</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.2259</v>
+        <v>-0.139</v>
       </c>
       <c r="E44" t="n">
         <v>0.6989</v>
@@ -2480,7 +2480,7 @@
         <v>0.2423</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.3346</v>
+        <v>-0.2576</v>
       </c>
       <c r="E45" t="n">
         <v>0.4053</v>
@@ -2526,7 +2526,7 @@
         <v>0.23</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.3422</v>
+        <v>-0.266</v>
       </c>
       <c r="E46" t="n">
         <v>0.3847</v>
@@ -2572,7 +2572,7 @@
         <v>0.2291</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.3427</v>
+        <v>-0.2665</v>
       </c>
       <c r="E47" t="n">
         <v>0.3833</v>
@@ -2618,7 +2618,7 @@
         <v>0.2102</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.3544</v>
+        <v>-0.2793</v>
       </c>
       <c r="E48" t="n">
         <v>0.3516</v>
@@ -2664,7 +2664,7 @@
         <v>0.1753</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.376</v>
+        <v>-0.3029</v>
       </c>
       <c r="E49" t="n">
         <v>0.2933</v>
@@ -2710,7 +2710,7 @@
         <v>0.1246</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.4074</v>
+        <v>-0.3371</v>
       </c>
       <c r="E50" t="n">
         <v>0.2085</v>
@@ -2756,7 +2756,7 @@
         <v>0.0433</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.4577</v>
+        <v>-0.3921</v>
       </c>
       <c r="E51" t="n">
         <v>0.07240000000000001</v>
@@ -2802,7 +2802,7 @@
         <v>-0.0035</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.4867</v>
+        <v>-0.4237</v>
       </c>
       <c r="E52" t="n">
         <v>-0.0058</v>
@@ -2848,7 +2848,7 @@
         <v>-0.0409</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.5098</v>
+        <v>-0.449</v>
       </c>
       <c r="E53" t="n">
         <v>-0.0684</v>
@@ -2894,7 +2894,7 @@
         <v>-0.0658</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.5252</v>
+        <v>-0.4658</v>
       </c>
       <c r="E54" t="n">
         <v>-0.11</v>
@@ -2940,7 +2940,7 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.5278</v>
+        <v>-0.4687</v>
       </c>
       <c r="E55" t="n">
         <v>-0.1171</v>
@@ -2986,7 +2986,7 @@
         <v>-0.1396</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.5709</v>
+        <v>-0.5157</v>
       </c>
       <c r="E56" t="n">
         <v>-0.2335</v>
@@ -3032,7 +3032,7 @@
         <v>-0.1889</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.6014</v>
+        <v>-0.549</v>
       </c>
       <c r="E57" t="n">
         <v>-0.3159</v>
@@ -3078,7 +3078,7 @@
         <v>-0.2844</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.6606</v>
+        <v>-0.6136</v>
       </c>
       <c r="E58" t="n">
         <v>-0.4758</v>
@@ -3124,7 +3124,7 @@
         <v>-0.3067</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.6744</v>
+        <v>-0.6286</v>
       </c>
       <c r="E59" t="n">
         <v>-0.5131</v>
@@ -3170,7 +3170,7 @@
         <v>-0.4155</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.7417</v>
+        <v>-0.7020999999999999</v>
       </c>
       <c r="E60" t="n">
         <v>-0.695</v>
@@ -3216,7 +3216,7 @@
         <v>-0.4319</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.7518</v>
+        <v>-0.7131999999999999</v>
       </c>
       <c r="E61" t="n">
         <v>-0.7224</v>
@@ -3262,7 +3262,7 @@
         <v>-0.4707</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.7759</v>
+        <v>-0.7395</v>
       </c>
       <c r="E62" t="n">
         <v>-0.7874</v>
@@ -3308,7 +3308,7 @@
         <v>-0.4911</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.7885</v>
+        <v>-0.7532</v>
       </c>
       <c r="E63" t="n">
         <v>-0.8215</v>
@@ -3354,7 +3354,7 @@
         <v>-0.5557</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.8284</v>
+        <v>-0.7969000000000001</v>
       </c>
       <c r="E64" t="n">
         <v>-0.9295</v>
@@ -3400,7 +3400,7 @@
         <v>-0.6518</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.8879</v>
+        <v>-0.8618</v>
       </c>
       <c r="E65" t="n">
         <v>-1.0902</v>
@@ -3446,7 +3446,7 @@
         <v>-0.7135</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.9261</v>
+        <v>-0.9035</v>
       </c>
       <c r="E66" t="n">
         <v>-1.1935</v>
@@ -3492,7 +3492,7 @@
         <v>-0.7271</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.9345</v>
+        <v>-0.9127</v>
       </c>
       <c r="E67" t="n">
         <v>-1.2162</v>
@@ -3538,7 +3538,7 @@
         <v>-0.7374000000000001</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.9409</v>
+        <v>-0.9196</v>
       </c>
       <c r="E68" t="n">
         <v>-1.2334</v>
@@ -3584,7 +3584,7 @@
         <v>-0.8779</v>
       </c>
       <c r="D69" t="n">
-        <v>-1.0279</v>
+        <v>-1.0146</v>
       </c>
       <c r="E69" t="n">
         <v>-1.4685</v>
@@ -3630,7 +3630,7 @@
         <v>-1.0204</v>
       </c>
       <c r="D70" t="n">
-        <v>-1.1161</v>
+        <v>-1.1109</v>
       </c>
       <c r="E70" t="n">
         <v>-1.7069</v>
@@ -3676,7 +3676,7 @@
         <v>-1.0493</v>
       </c>
       <c r="D71" t="n">
-        <v>-1.1339</v>
+        <v>-1.1304</v>
       </c>
       <c r="E71" t="n">
         <v>-1.7552</v>
@@ -3722,7 +3722,7 @@
         <v>-1.1517</v>
       </c>
       <c r="D72" t="n">
-        <v>-1.1973</v>
+        <v>-1.1996</v>
       </c>
       <c r="E72" t="n">
         <v>-1.9265</v>
@@ -3768,7 +3768,7 @@
         <v>-1.3937</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.3471</v>
+        <v>-1.3631</v>
       </c>
       <c r="E73" t="n">
         <v>-2.3312</v>
@@ -3814,7 +3814,7 @@
         <v>-1.4797</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.4003</v>
+        <v>-1.4213</v>
       </c>
       <c r="E74" t="n">
         <v>-2.4752</v>
@@ -3860,7 +3860,7 @@
         <v>-1.6545</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.5085</v>
+        <v>-1.5394</v>
       </c>
       <c r="E75" t="n">
         <v>-2.7675</v>
@@ -3906,7 +3906,7 @@
         <v>-1.6676</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.5166</v>
+        <v>-1.5482</v>
       </c>
       <c r="E76" t="n">
         <v>-2.7894</v>
@@ -3952,7 +3952,7 @@
         <v>-1.8504</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.6297</v>
+        <v>-1.6718</v>
       </c>
       <c r="E77" t="n">
         <v>-3.0952</v>
@@ -3998,7 +3998,7 @@
         <v>-1.9009</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.661</v>
+        <v>-1.7059</v>
       </c>
       <c r="E78" t="n">
         <v>-3.1797</v>
@@ -4044,7 +4044,7 @@
         <v>-2.3338</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.9289</v>
+        <v>-1.9984</v>
       </c>
       <c r="E79" t="n">
         <v>-3.9038</v>
@@ -4090,7 +4090,7 @@
         <v>-2.67</v>
       </c>
       <c r="D80" t="n">
-        <v>-2.137</v>
+        <v>-2.2256</v>
       </c>
       <c r="E80" t="n">
         <v>-4.4662</v>
@@ -4136,7 +4136,7 @@
         <v>-5.3276</v>
       </c>
       <c r="D81" t="n">
-        <v>-3.7818</v>
+        <v>-4.0215</v>
       </c>
       <c r="E81" t="n">
         <v>-8.9116</v>

--- a/database/event/8301/event_8301_evp_summary.xlsx
+++ b/database/event/8301/event_8301_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>5.8935</v>
       </c>
       <c r="D2" t="n">
-        <v>3.5611</v>
+        <v>3.4836</v>
       </c>
       <c r="E2" t="n">
         <v>9.8582</v>
@@ -548,7 +548,7 @@
         <v>5.4851</v>
       </c>
       <c r="D3" t="n">
-        <v>3.2852</v>
+        <v>3.2115</v>
       </c>
       <c r="E3" t="n">
         <v>9.1751</v>
@@ -594,7 +594,7 @@
         <v>4.6915</v>
       </c>
       <c r="D4" t="n">
-        <v>2.7489</v>
+        <v>2.6826</v>
       </c>
       <c r="E4" t="n">
         <v>7.8476</v>
@@ -640,7 +640,7 @@
         <v>4.259</v>
       </c>
       <c r="D5" t="n">
-        <v>2.4566</v>
+        <v>2.3943</v>
       </c>
       <c r="E5" t="n">
         <v>7.1241</v>
@@ -686,7 +686,7 @@
         <v>4.0461</v>
       </c>
       <c r="D6" t="n">
-        <v>2.3128</v>
+        <v>2.2525</v>
       </c>
       <c r="E6" t="n">
         <v>6.768</v>
@@ -726,25 +726,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.7644</v>
+        <v>6.7526</v>
       </c>
       <c r="C7" t="n">
-        <v>4.0439</v>
+        <v>4.0369</v>
       </c>
       <c r="D7" t="n">
-        <v>2.3113</v>
+        <v>2.2463</v>
       </c>
       <c r="E7" t="n">
-        <v>6.7644</v>
+        <v>6.7526</v>
       </c>
       <c r="F7" t="n">
-        <v>4.6467</v>
+        <v>4.6348</v>
       </c>
       <c r="G7" t="n">
         <v>2.1177</v>
       </c>
       <c r="H7" t="n">
-        <v>4.9829</v>
+        <v>4.9643</v>
       </c>
       <c r="I7" t="n">
         <v>5.0061</v>
@@ -778,7 +778,7 @@
         <v>3.9337</v>
       </c>
       <c r="D8" t="n">
-        <v>2.2368</v>
+        <v>2.1776</v>
       </c>
       <c r="E8" t="n">
         <v>6.58</v>
@@ -818,25 +818,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.4908</v>
+        <v>6.4755</v>
       </c>
       <c r="C9" t="n">
-        <v>3.8804</v>
+        <v>3.8712</v>
       </c>
       <c r="D9" t="n">
-        <v>2.2008</v>
+        <v>2.1359</v>
       </c>
       <c r="E9" t="n">
-        <v>6.4908</v>
+        <v>6.4755</v>
       </c>
       <c r="F9" t="n">
-        <v>5.5772</v>
+        <v>5.5619</v>
       </c>
       <c r="G9" t="n">
         <v>0.9136</v>
       </c>
       <c r="H9" t="n">
-        <v>6.442</v>
+        <v>6.418</v>
       </c>
       <c r="I9" t="n">
         <v>6.472</v>
@@ -870,7 +870,7 @@
         <v>3.7882</v>
       </c>
       <c r="D10" t="n">
-        <v>2.1385</v>
+        <v>2.0806</v>
       </c>
       <c r="E10" t="n">
         <v>6.3366</v>
@@ -916,7 +916,7 @@
         <v>3.7523</v>
       </c>
       <c r="D11" t="n">
-        <v>2.1142</v>
+        <v>2.0566</v>
       </c>
       <c r="E11" t="n">
         <v>6.2765</v>
@@ -956,25 +956,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6.0239</v>
+        <v>6.0091</v>
       </c>
       <c r="C12" t="n">
-        <v>3.6013</v>
+        <v>3.5924</v>
       </c>
       <c r="D12" t="n">
-        <v>2.0122</v>
+        <v>1.9501</v>
       </c>
       <c r="E12" t="n">
-        <v>6.0239</v>
+        <v>6.0091</v>
       </c>
       <c r="F12" t="n">
-        <v>5.4364</v>
+        <v>5.4216</v>
       </c>
       <c r="G12" t="n">
         <v>0.5875</v>
       </c>
       <c r="H12" t="n">
-        <v>6.2212</v>
+        <v>6.198</v>
       </c>
       <c r="I12" t="n">
         <v>6.2502</v>
@@ -1008,7 +1008,7 @@
         <v>2.9321</v>
       </c>
       <c r="D13" t="n">
-        <v>1.56</v>
+        <v>1.5101</v>
       </c>
       <c r="E13" t="n">
         <v>4.9046</v>
@@ -1054,7 +1054,7 @@
         <v>2.7815</v>
       </c>
       <c r="D14" t="n">
-        <v>1.4582</v>
+        <v>1.4097</v>
       </c>
       <c r="E14" t="n">
         <v>4.6526</v>
@@ -1094,25 +1094,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.4195</v>
+        <v>4.4063</v>
       </c>
       <c r="C15" t="n">
-        <v>2.6421</v>
+        <v>2.6342</v>
       </c>
       <c r="D15" t="n">
-        <v>1.364</v>
+        <v>1.3116</v>
       </c>
       <c r="E15" t="n">
-        <v>4.4195</v>
+        <v>4.4063</v>
       </c>
       <c r="F15" t="n">
-        <v>3.5573</v>
+        <v>3.5441</v>
       </c>
       <c r="G15" t="n">
         <v>0.8622</v>
       </c>
       <c r="H15" t="n">
-        <v>3.5573</v>
+        <v>3.5441</v>
       </c>
       <c r="I15" t="n">
         <v>3.5739</v>
@@ -1146,7 +1146,7 @@
         <v>2.0743</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9802999999999999</v>
+        <v>0.9384</v>
       </c>
       <c r="E16" t="n">
         <v>3.4697</v>
@@ -1186,25 +1186,25 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3.3718</v>
+        <v>3.3601</v>
       </c>
       <c r="C17" t="n">
-        <v>2.0158</v>
+        <v>2.0088</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9408</v>
+        <v>0.8948</v>
       </c>
       <c r="E17" t="n">
-        <v>3.3718</v>
+        <v>3.3601</v>
       </c>
       <c r="F17" t="n">
-        <v>3.1473</v>
+        <v>3.1356</v>
       </c>
       <c r="G17" t="n">
         <v>0.2245</v>
       </c>
       <c r="H17" t="n">
-        <v>3.1473</v>
+        <v>3.1356</v>
       </c>
       <c r="I17" t="n">
         <v>3.1619</v>
@@ -1238,7 +1238,7 @@
         <v>1.9958</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9273</v>
+        <v>0.8861</v>
       </c>
       <c r="E18" t="n">
         <v>3.3384</v>
@@ -1278,25 +1278,25 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.105</v>
+        <v>3.099</v>
       </c>
       <c r="C19" t="n">
-        <v>1.8563</v>
+        <v>1.8527</v>
       </c>
       <c r="D19" t="n">
-        <v>0.833</v>
+        <v>0.7907</v>
       </c>
       <c r="E19" t="n">
-        <v>3.105</v>
+        <v>3.099</v>
       </c>
       <c r="F19" t="n">
-        <v>1.6109</v>
+        <v>1.6049</v>
       </c>
       <c r="G19" t="n">
         <v>1.4941</v>
       </c>
       <c r="H19" t="n">
-        <v>1.6109</v>
+        <v>1.6049</v>
       </c>
       <c r="I19" t="n">
         <v>1.6184</v>
@@ -1330,7 +1330,7 @@
         <v>1.6318</v>
       </c>
       <c r="D20" t="n">
-        <v>0.6813</v>
+        <v>0.6435</v>
       </c>
       <c r="E20" t="n">
         <v>2.7295</v>
@@ -1376,7 +1376,7 @@
         <v>1.6138</v>
       </c>
       <c r="D21" t="n">
-        <v>0.6691</v>
+        <v>0.6315</v>
       </c>
       <c r="E21" t="n">
         <v>2.6994</v>
@@ -1422,7 +1422,7 @@
         <v>1.5689</v>
       </c>
       <c r="D22" t="n">
-        <v>0.6388</v>
+        <v>0.6016</v>
       </c>
       <c r="E22" t="n">
         <v>2.6243</v>
@@ -1468,7 +1468,7 @@
         <v>1.5482</v>
       </c>
       <c r="D23" t="n">
-        <v>0.6248</v>
+        <v>0.5878</v>
       </c>
       <c r="E23" t="n">
         <v>2.5897</v>
@@ -1514,7 +1514,7 @@
         <v>1.5194</v>
       </c>
       <c r="D24" t="n">
-        <v>0.6052999999999999</v>
+        <v>0.5686</v>
       </c>
       <c r="E24" t="n">
         <v>2.5415</v>
@@ -1560,7 +1560,7 @@
         <v>1.5123</v>
       </c>
       <c r="D25" t="n">
-        <v>0.6005</v>
+        <v>0.5639</v>
       </c>
       <c r="E25" t="n">
         <v>2.5296</v>
@@ -1606,7 +1606,7 @@
         <v>1.4991</v>
       </c>
       <c r="D26" t="n">
-        <v>0.5917</v>
+        <v>0.5551</v>
       </c>
       <c r="E26" t="n">
         <v>2.5076</v>
@@ -1646,25 +1646,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2.3899</v>
+        <v>2.3866</v>
       </c>
       <c r="C27" t="n">
-        <v>1.4287</v>
+        <v>1.4268</v>
       </c>
       <c r="D27" t="n">
-        <v>0.5441</v>
+        <v>0.5069</v>
       </c>
       <c r="E27" t="n">
-        <v>2.3899</v>
+        <v>2.3866</v>
       </c>
       <c r="F27" t="n">
-        <v>0.872</v>
+        <v>0.8687</v>
       </c>
       <c r="G27" t="n">
         <v>1.5179</v>
       </c>
       <c r="H27" t="n">
-        <v>0.872</v>
+        <v>0.8687</v>
       </c>
       <c r="I27" t="n">
         <v>0.876</v>
@@ -1692,25 +1692,25 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.2944</v>
+        <v>2.2817</v>
       </c>
       <c r="C28" t="n">
-        <v>1.3717</v>
+        <v>1.3641</v>
       </c>
       <c r="D28" t="n">
-        <v>0.5054999999999999</v>
+        <v>0.4651</v>
       </c>
       <c r="E28" t="n">
-        <v>2.2944</v>
+        <v>2.2817</v>
       </c>
       <c r="F28" t="n">
-        <v>3.4139</v>
+        <v>3.4012</v>
       </c>
       <c r="G28" t="n">
         <v>-1.1195</v>
       </c>
       <c r="H28" t="n">
-        <v>3.4139</v>
+        <v>3.4012</v>
       </c>
       <c r="I28" t="n">
         <v>3.4298</v>
@@ -1744,7 +1744,7 @@
         <v>1.3564</v>
       </c>
       <c r="D29" t="n">
-        <v>0.4952</v>
+        <v>0.46</v>
       </c>
       <c r="E29" t="n">
         <v>2.2688</v>
@@ -1784,25 +1784,25 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.897</v>
+        <v>1.8894</v>
       </c>
       <c r="C30" t="n">
-        <v>1.1341</v>
+        <v>1.1295</v>
       </c>
       <c r="D30" t="n">
-        <v>0.345</v>
+        <v>0.3088</v>
       </c>
       <c r="E30" t="n">
-        <v>1.897</v>
+        <v>1.8894</v>
       </c>
       <c r="F30" t="n">
-        <v>2.0385</v>
+        <v>2.0309</v>
       </c>
       <c r="G30" t="n">
         <v>-0.1415</v>
       </c>
       <c r="H30" t="n">
-        <v>2.0385</v>
+        <v>2.0309</v>
       </c>
       <c r="I30" t="n">
         <v>2.048</v>
@@ -1830,25 +1830,25 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.746</v>
+        <v>1.7383</v>
       </c>
       <c r="C31" t="n">
-        <v>1.0438</v>
+        <v>1.0392</v>
       </c>
       <c r="D31" t="n">
-        <v>0.284</v>
+        <v>0.2486</v>
       </c>
       <c r="E31" t="n">
-        <v>1.746</v>
+        <v>1.7383</v>
       </c>
       <c r="F31" t="n">
-        <v>2.0723</v>
+        <v>2.0646</v>
       </c>
       <c r="G31" t="n">
         <v>-0.3263</v>
       </c>
       <c r="H31" t="n">
-        <v>2.0723</v>
+        <v>2.0646</v>
       </c>
       <c r="I31" t="n">
         <v>2.0819</v>
@@ -1882,7 +1882,7 @@
         <v>0.9875</v>
       </c>
       <c r="D32" t="n">
-        <v>0.2459</v>
+        <v>0.2142</v>
       </c>
       <c r="E32" t="n">
         <v>1.6518</v>
@@ -1922,25 +1922,25 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.5268</v>
+        <v>1.5206</v>
       </c>
       <c r="C33" t="n">
-        <v>0.9127999999999999</v>
+        <v>0.9091</v>
       </c>
       <c r="D33" t="n">
-        <v>0.1954</v>
+        <v>0.1619</v>
       </c>
       <c r="E33" t="n">
-        <v>1.5268</v>
+        <v>1.5206</v>
       </c>
       <c r="F33" t="n">
-        <v>1.6563</v>
+        <v>1.6501</v>
       </c>
       <c r="G33" t="n">
         <v>-0.1295</v>
       </c>
       <c r="H33" t="n">
-        <v>1.6563</v>
+        <v>1.6501</v>
       </c>
       <c r="I33" t="n">
         <v>1.664</v>
@@ -1974,7 +1974,7 @@
         <v>0.9025</v>
       </c>
       <c r="D34" t="n">
-        <v>0.1885</v>
+        <v>0.1576</v>
       </c>
       <c r="E34" t="n">
         <v>1.5097</v>
@@ -2020,7 +2020,7 @@
         <v>0.8018999999999999</v>
       </c>
       <c r="D35" t="n">
-        <v>0.1205</v>
+        <v>0.0905</v>
       </c>
       <c r="E35" t="n">
         <v>1.3413</v>
@@ -2066,7 +2066,7 @@
         <v>0.7796999999999999</v>
       </c>
       <c r="D36" t="n">
-        <v>0.1055</v>
+        <v>0.0757</v>
       </c>
       <c r="E36" t="n">
         <v>1.3043</v>
@@ -2112,7 +2112,7 @@
         <v>0.6886</v>
       </c>
       <c r="D37" t="n">
-        <v>0.044</v>
+        <v>0.015</v>
       </c>
       <c r="E37" t="n">
         <v>1.1519</v>
@@ -2158,7 +2158,7 @@
         <v>0.6596</v>
       </c>
       <c r="D38" t="n">
-        <v>0.0243</v>
+        <v>-0.0044</v>
       </c>
       <c r="E38" t="n">
         <v>1.1033</v>
@@ -2204,7 +2204,7 @@
         <v>0.6238</v>
       </c>
       <c r="D39" t="n">
-        <v>0.0001</v>
+        <v>-0.0282</v>
       </c>
       <c r="E39" t="n">
         <v>1.0434</v>
@@ -2250,7 +2250,7 @@
         <v>0.6176</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.004</v>
+        <v>-0.0323</v>
       </c>
       <c r="E40" t="n">
         <v>1.0331</v>
@@ -2296,7 +2296,7 @@
         <v>0.5635</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.0406</v>
+        <v>-0.0684</v>
       </c>
       <c r="E41" t="n">
         <v>0.9425</v>
@@ -2336,25 +2336,25 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.9036999999999999</v>
+        <v>0.9023</v>
       </c>
       <c r="C42" t="n">
-        <v>0.5403</v>
+        <v>0.5394</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.0563</v>
+        <v>-0.0844</v>
       </c>
       <c r="E42" t="n">
-        <v>0.9036999999999999</v>
+        <v>0.9023</v>
       </c>
       <c r="F42" t="n">
-        <v>0.3743</v>
+        <v>0.3729</v>
       </c>
       <c r="G42" t="n">
         <v>0.5294</v>
       </c>
       <c r="H42" t="n">
-        <v>0.3743</v>
+        <v>0.3729</v>
       </c>
       <c r="I42" t="n">
         <v>0.376</v>
@@ -2382,25 +2382,25 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.7707000000000001</v>
+        <v>0.7682</v>
       </c>
       <c r="C43" t="n">
-        <v>0.4607</v>
+        <v>0.4593</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.11</v>
+        <v>-0.1379</v>
       </c>
       <c r="E43" t="n">
-        <v>0.7707000000000001</v>
+        <v>0.7682</v>
       </c>
       <c r="F43" t="n">
-        <v>0.6829</v>
+        <v>0.6804</v>
       </c>
       <c r="G43" t="n">
         <v>0.0878</v>
       </c>
       <c r="H43" t="n">
-        <v>0.6829</v>
+        <v>0.6804</v>
       </c>
       <c r="I43" t="n">
         <v>0.6861</v>
@@ -2434,7 +2434,7 @@
         <v>0.4178</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.139</v>
+        <v>-0.1655</v>
       </c>
       <c r="E44" t="n">
         <v>0.6989</v>
@@ -2480,7 +2480,7 @@
         <v>0.2423</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.2576</v>
+        <v>-0.2824</v>
       </c>
       <c r="E45" t="n">
         <v>0.4053</v>
@@ -2526,7 +2526,7 @@
         <v>0.23</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.266</v>
+        <v>-0.2906</v>
       </c>
       <c r="E46" t="n">
         <v>0.3847</v>
@@ -2572,7 +2572,7 @@
         <v>0.2291</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.2665</v>
+        <v>-0.2912</v>
       </c>
       <c r="E47" t="n">
         <v>0.3833</v>
@@ -2612,25 +2612,25 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.3516</v>
+        <v>0.3482</v>
       </c>
       <c r="C48" t="n">
-        <v>0.2102</v>
+        <v>0.2082</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.2793</v>
+        <v>-0.3052</v>
       </c>
       <c r="E48" t="n">
-        <v>0.3516</v>
+        <v>0.3482</v>
       </c>
       <c r="F48" t="n">
-        <v>0.9153</v>
+        <v>0.9119</v>
       </c>
       <c r="G48" t="n">
         <v>-0.5637</v>
       </c>
       <c r="H48" t="n">
-        <v>0.9153</v>
+        <v>0.9119</v>
       </c>
       <c r="I48" t="n">
         <v>0.9196</v>
@@ -2664,7 +2664,7 @@
         <v>0.1753</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.3029</v>
+        <v>-0.3271</v>
       </c>
       <c r="E49" t="n">
         <v>0.2933</v>
@@ -2710,7 +2710,7 @@
         <v>0.1246</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.3371</v>
+        <v>-0.3608</v>
       </c>
       <c r="E50" t="n">
         <v>0.2085</v>
@@ -2756,7 +2756,7 @@
         <v>0.0433</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.3921</v>
+        <v>-0.4151</v>
       </c>
       <c r="E51" t="n">
         <v>0.07240000000000001</v>
@@ -2802,7 +2802,7 @@
         <v>-0.0035</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.4237</v>
+        <v>-0.4462</v>
       </c>
       <c r="E52" t="n">
         <v>-0.0058</v>
@@ -2842,25 +2842,25 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.0684</v>
+        <v>-0.06569999999999999</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.0409</v>
+        <v>-0.0393</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.449</v>
+        <v>-0.4701</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.0684</v>
+        <v>-0.06569999999999999</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.7118</v>
+        <v>-0.7091</v>
       </c>
       <c r="G53" t="n">
         <v>0.6434</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.7118</v>
+        <v>-0.7091</v>
       </c>
       <c r="I53" t="n">
         <v>-0.7151</v>
@@ -2894,7 +2894,7 @@
         <v>-0.0658</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.4658</v>
+        <v>-0.4877</v>
       </c>
       <c r="E54" t="n">
         <v>-0.11</v>
@@ -2940,7 +2940,7 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.4687</v>
+        <v>-0.4906</v>
       </c>
       <c r="E55" t="n">
         <v>-0.1171</v>
@@ -2986,7 +2986,7 @@
         <v>-0.1396</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.5157</v>
+        <v>-0.5369</v>
       </c>
       <c r="E56" t="n">
         <v>-0.2335</v>
@@ -3026,25 +3026,25 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-0.3159</v>
+        <v>-0.317</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.1889</v>
+        <v>-0.1895</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.549</v>
+        <v>-0.5702</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.3159</v>
+        <v>-0.317</v>
       </c>
       <c r="F57" t="n">
-        <v>0.2867</v>
+        <v>0.2856</v>
       </c>
       <c r="G57" t="n">
         <v>-0.6026</v>
       </c>
       <c r="H57" t="n">
-        <v>0.2867</v>
+        <v>0.2856</v>
       </c>
       <c r="I57" t="n">
         <v>0.288</v>
@@ -3072,25 +3072,25 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-0.4758</v>
+        <v>-0.4747</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.2844</v>
+        <v>-0.2838</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.6136</v>
+        <v>-0.633</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.4758</v>
+        <v>-0.4747</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.2804</v>
+        <v>-0.2793</v>
       </c>
       <c r="G58" t="n">
         <v>-0.1954</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.2804</v>
+        <v>-0.2793</v>
       </c>
       <c r="I58" t="n">
         <v>-0.2817</v>
@@ -3124,7 +3124,7 @@
         <v>-0.3067</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.6286</v>
+        <v>-0.6483</v>
       </c>
       <c r="E59" t="n">
         <v>-0.5131</v>
@@ -3170,7 +3170,7 @@
         <v>-0.4155</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.7020999999999999</v>
+        <v>-0.7208</v>
       </c>
       <c r="E60" t="n">
         <v>-0.695</v>
@@ -3216,7 +3216,7 @@
         <v>-0.4319</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.7131999999999999</v>
+        <v>-0.7317</v>
       </c>
       <c r="E61" t="n">
         <v>-0.7224</v>
@@ -3262,7 +3262,7 @@
         <v>-0.4707</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.7395</v>
+        <v>-0.7576000000000001</v>
       </c>
       <c r="E62" t="n">
         <v>-0.7874</v>
@@ -3308,7 +3308,7 @@
         <v>-0.4911</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.7532</v>
+        <v>-0.7712</v>
       </c>
       <c r="E63" t="n">
         <v>-0.8215</v>
@@ -3354,7 +3354,7 @@
         <v>-0.5557</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.7969000000000001</v>
+        <v>-0.8142</v>
       </c>
       <c r="E64" t="n">
         <v>-0.9295</v>
@@ -3400,7 +3400,7 @@
         <v>-0.6518</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.8618</v>
+        <v>-0.8782</v>
       </c>
       <c r="E65" t="n">
         <v>-1.0902</v>
@@ -3446,7 +3446,7 @@
         <v>-0.7135</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.9035</v>
+        <v>-0.9194</v>
       </c>
       <c r="E66" t="n">
         <v>-1.1935</v>
@@ -3492,7 +3492,7 @@
         <v>-0.7271</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.9127</v>
+        <v>-0.9284</v>
       </c>
       <c r="E67" t="n">
         <v>-1.2162</v>
@@ -3538,7 +3538,7 @@
         <v>-0.7374000000000001</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.9196</v>
+        <v>-0.9353</v>
       </c>
       <c r="E68" t="n">
         <v>-1.2334</v>
@@ -3584,7 +3584,7 @@
         <v>-0.8779</v>
       </c>
       <c r="D69" t="n">
-        <v>-1.0146</v>
+        <v>-1.029</v>
       </c>
       <c r="E69" t="n">
         <v>-1.4685</v>
@@ -3630,7 +3630,7 @@
         <v>-1.0204</v>
       </c>
       <c r="D70" t="n">
-        <v>-1.1109</v>
+        <v>-1.1239</v>
       </c>
       <c r="E70" t="n">
         <v>-1.7069</v>
@@ -3676,7 +3676,7 @@
         <v>-1.0493</v>
       </c>
       <c r="D71" t="n">
-        <v>-1.1304</v>
+        <v>-1.1432</v>
       </c>
       <c r="E71" t="n">
         <v>-1.7552</v>
@@ -3716,25 +3716,25 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-1.9265</v>
+        <v>-1.9215</v>
       </c>
       <c r="C72" t="n">
-        <v>-1.1517</v>
+        <v>-1.1487</v>
       </c>
       <c r="D72" t="n">
-        <v>-1.1996</v>
+        <v>-1.2094</v>
       </c>
       <c r="E72" t="n">
-        <v>-1.9265</v>
+        <v>-1.9215</v>
       </c>
       <c r="F72" t="n">
-        <v>-1.3374</v>
+        <v>-1.3324</v>
       </c>
       <c r="G72" t="n">
         <v>-0.5891</v>
       </c>
       <c r="H72" t="n">
-        <v>-1.3374</v>
+        <v>-1.3324</v>
       </c>
       <c r="I72" t="n">
         <v>-1.3436</v>
@@ -3768,7 +3768,7 @@
         <v>-1.3937</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.3631</v>
+        <v>-1.3727</v>
       </c>
       <c r="E73" t="n">
         <v>-2.3312</v>
@@ -3814,7 +3814,7 @@
         <v>-1.4797</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.4213</v>
+        <v>-1.43</v>
       </c>
       <c r="E74" t="n">
         <v>-2.4752</v>
@@ -3854,25 +3854,25 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-2.7675</v>
+        <v>-2.7567</v>
       </c>
       <c r="C75" t="n">
-        <v>-1.6545</v>
+        <v>-1.648</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.5394</v>
+        <v>-1.5422</v>
       </c>
       <c r="E75" t="n">
-        <v>-2.7675</v>
+        <v>-2.7567</v>
       </c>
       <c r="F75" t="n">
-        <v>-2.9147</v>
+        <v>-2.9039</v>
       </c>
       <c r="G75" t="n">
         <v>0.1472</v>
       </c>
       <c r="H75" t="n">
-        <v>-2.9147</v>
+        <v>-2.9039</v>
       </c>
       <c r="I75" t="n">
         <v>-2.9283</v>
@@ -3906,7 +3906,7 @@
         <v>-1.6676</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.5482</v>
+        <v>-1.5552</v>
       </c>
       <c r="E76" t="n">
         <v>-2.7894</v>
@@ -3952,7 +3952,7 @@
         <v>-1.8504</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.6718</v>
+        <v>-1.677</v>
       </c>
       <c r="E77" t="n">
         <v>-3.0952</v>
@@ -3992,25 +3992,25 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-3.1797</v>
+        <v>-3.1702</v>
       </c>
       <c r="C78" t="n">
-        <v>-1.9009</v>
+        <v>-1.8952</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.7059</v>
+        <v>-1.7069</v>
       </c>
       <c r="E78" t="n">
-        <v>-3.1797</v>
+        <v>-3.1702</v>
       </c>
       <c r="F78" t="n">
-        <v>-2.5376</v>
+        <v>-2.5281</v>
       </c>
       <c r="G78" t="n">
         <v>-0.6421</v>
       </c>
       <c r="H78" t="n">
-        <v>-2.5376</v>
+        <v>-2.5281</v>
       </c>
       <c r="I78" t="n">
         <v>-2.5494</v>
@@ -4044,7 +4044,7 @@
         <v>-2.3338</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.9984</v>
+        <v>-1.9992</v>
       </c>
       <c r="E79" t="n">
         <v>-3.9038</v>
@@ -4090,7 +4090,7 @@
         <v>-2.67</v>
       </c>
       <c r="D80" t="n">
-        <v>-2.2256</v>
+        <v>-2.2232</v>
       </c>
       <c r="E80" t="n">
         <v>-4.4662</v>
@@ -4136,7 +4136,7 @@
         <v>-5.3276</v>
       </c>
       <c r="D81" t="n">
-        <v>-4.0215</v>
+        <v>-3.9943</v>
       </c>
       <c r="E81" t="n">
         <v>-8.9116</v>

--- a/database/event/8301/event_8301_evp_summary.xlsx
+++ b/database/event/8301/event_8301_evp_summary.xlsx
@@ -496,16 +496,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.614699999999999</v>
+        <v>8.9316</v>
       </c>
       <c r="C2" t="n">
-        <v>5.1501</v>
+        <v>5.3396</v>
       </c>
       <c r="D2" t="n">
-        <v>3.2974</v>
+        <v>3.3757</v>
       </c>
       <c r="E2" t="n">
-        <v>8.614699999999999</v>
+        <v>8.9316</v>
       </c>
       <c r="F2" t="n">
         <v>4.2665</v>
@@ -542,16 +542,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.439</v>
+        <v>8.529199999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>5.0451</v>
+        <v>5.099</v>
       </c>
       <c r="D3" t="n">
-        <v>3.2174</v>
+        <v>3.196</v>
       </c>
       <c r="E3" t="n">
-        <v>8.439</v>
+        <v>8.529199999999999</v>
       </c>
       <c r="F3" t="n">
         <v>4.0668</v>
@@ -588,16 +588,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8.193</v>
+        <v>8.3246</v>
       </c>
       <c r="C4" t="n">
-        <v>4.898</v>
+        <v>4.9767</v>
       </c>
       <c r="D4" t="n">
-        <v>3.1054</v>
+        <v>3.1046</v>
       </c>
       <c r="E4" t="n">
-        <v>8.193</v>
+        <v>8.3246</v>
       </c>
       <c r="F4" t="n">
         <v>1.8907</v>
@@ -634,16 +634,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.0759</v>
+        <v>7.3281</v>
       </c>
       <c r="C5" t="n">
-        <v>4.2302</v>
+        <v>4.3809</v>
       </c>
       <c r="D5" t="n">
-        <v>2.5969</v>
+        <v>2.6595</v>
       </c>
       <c r="E5" t="n">
-        <v>7.0759</v>
+        <v>7.3281</v>
       </c>
       <c r="F5" t="n">
         <v>5.0899</v>
@@ -680,16 +680,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.5576</v>
+        <v>7.0186</v>
       </c>
       <c r="C6" t="n">
-        <v>3.9203</v>
+        <v>4.1959</v>
       </c>
       <c r="D6" t="n">
-        <v>2.361</v>
+        <v>2.5212</v>
       </c>
       <c r="E6" t="n">
-        <v>6.5576</v>
+        <v>7.0186</v>
       </c>
       <c r="F6" t="n">
         <v>6.0516</v>
@@ -726,16 +726,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.4172</v>
+        <v>6.6585</v>
       </c>
       <c r="C7" t="n">
-        <v>3.8364</v>
+        <v>3.9806</v>
       </c>
       <c r="D7" t="n">
-        <v>2.297</v>
+        <v>2.3604</v>
       </c>
       <c r="E7" t="n">
-        <v>6.4172</v>
+        <v>6.6585</v>
       </c>
       <c r="F7" t="n">
         <v>3.6724</v>
@@ -768,185 +768,185 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HeavyGod</t>
+          <t>sh1ro</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.9674</v>
+        <v>6.1862</v>
       </c>
       <c r="C8" t="n">
-        <v>3.5675</v>
+        <v>3.6983</v>
       </c>
       <c r="D8" t="n">
-        <v>2.0923</v>
+        <v>2.1494</v>
       </c>
       <c r="E8" t="n">
-        <v>5.9674</v>
+        <v>6.1862</v>
       </c>
       <c r="F8" t="n">
-        <v>5.0507</v>
+        <v>4.0058</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9167</v>
+        <v>1.8125</v>
       </c>
       <c r="H8" t="n">
-        <v>8.3294</v>
+        <v>6.0426</v>
       </c>
       <c r="I8" t="n">
-        <v>8.544</v>
+        <v>6.0426</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9167</v>
+        <v>1.8125</v>
       </c>
       <c r="K8" t="n">
-        <v>287</v>
+        <v>179</v>
       </c>
       <c r="L8" t="n">
-        <v>99</v>
+        <v>178</v>
       </c>
       <c r="M8" t="n">
-        <v>9.460700000000001</v>
+        <v>7.8551</v>
       </c>
       <c r="N8" t="n">
-        <v>386</v>
+        <v>357</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>sh1ro</t>
+          <t>HeavyGod</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.8183</v>
+        <v>6.0538</v>
       </c>
       <c r="C9" t="n">
-        <v>3.4783</v>
+        <v>3.6191</v>
       </c>
       <c r="D9" t="n">
-        <v>2.0244</v>
+        <v>2.0903</v>
       </c>
       <c r="E9" t="n">
-        <v>5.8183</v>
+        <v>6.0538</v>
       </c>
       <c r="F9" t="n">
-        <v>4.0058</v>
+        <v>5.0507</v>
       </c>
       <c r="G9" t="n">
-        <v>1.8125</v>
+        <v>0.9167</v>
       </c>
       <c r="H9" t="n">
-        <v>6.0426</v>
+        <v>8.3294</v>
       </c>
       <c r="I9" t="n">
-        <v>6.0426</v>
+        <v>8.544</v>
       </c>
       <c r="J9" t="n">
-        <v>1.8125</v>
+        <v>0.9167</v>
       </c>
       <c r="K9" t="n">
-        <v>179</v>
+        <v>287</v>
       </c>
       <c r="L9" t="n">
-        <v>178</v>
+        <v>99</v>
       </c>
       <c r="M9" t="n">
-        <v>7.8551</v>
+        <v>9.460700000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>357</v>
+        <v>386</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>yuurih</t>
+          <t>Wicadia</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5.7607</v>
+        <v>5.8627</v>
       </c>
       <c r="C10" t="n">
-        <v>3.4439</v>
+        <v>3.5049</v>
       </c>
       <c r="D10" t="n">
-        <v>1.9982</v>
+        <v>2.0049</v>
       </c>
       <c r="E10" t="n">
-        <v>5.7607</v>
+        <v>5.8627</v>
       </c>
       <c r="F10" t="n">
-        <v>2.9197</v>
+        <v>3.7496</v>
       </c>
       <c r="G10" t="n">
-        <v>2.841</v>
+        <v>1.8868</v>
       </c>
       <c r="H10" t="n">
-        <v>3.6654</v>
+        <v>5.4818</v>
       </c>
       <c r="I10" t="n">
-        <v>3.6654</v>
+        <v>5.6231</v>
       </c>
       <c r="J10" t="n">
-        <v>2.841</v>
+        <v>1.8868</v>
       </c>
       <c r="K10" t="n">
-        <v>134</v>
+        <v>173</v>
       </c>
       <c r="L10" t="n">
-        <v>164</v>
+        <v>80</v>
       </c>
       <c r="M10" t="n">
-        <v>6.5064</v>
+        <v>7.5099</v>
       </c>
       <c r="N10" t="n">
-        <v>298</v>
+        <v>253</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Wicadia</t>
+          <t>yuurih</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5.6364</v>
+        <v>5.8518</v>
       </c>
       <c r="C11" t="n">
-        <v>3.3696</v>
+        <v>3.4984</v>
       </c>
       <c r="D11" t="n">
-        <v>1.9416</v>
+        <v>2.0001</v>
       </c>
       <c r="E11" t="n">
-        <v>5.6364</v>
+        <v>5.8518</v>
       </c>
       <c r="F11" t="n">
-        <v>3.7496</v>
+        <v>2.9197</v>
       </c>
       <c r="G11" t="n">
-        <v>1.8868</v>
+        <v>2.841</v>
       </c>
       <c r="H11" t="n">
-        <v>5.4818</v>
+        <v>3.6654</v>
       </c>
       <c r="I11" t="n">
-        <v>5.6231</v>
+        <v>3.6654</v>
       </c>
       <c r="J11" t="n">
-        <v>1.8868</v>
+        <v>2.841</v>
       </c>
       <c r="K11" t="n">
-        <v>173</v>
+        <v>134</v>
       </c>
       <c r="L11" t="n">
-        <v>80</v>
+        <v>164</v>
       </c>
       <c r="M11" t="n">
-        <v>7.5099</v>
+        <v>6.5064</v>
       </c>
       <c r="N11" t="n">
-        <v>253</v>
+        <v>298</v>
       </c>
     </row>
     <row r="12">
@@ -956,16 +956,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5.5782</v>
+        <v>5.7632</v>
       </c>
       <c r="C12" t="n">
-        <v>3.3348</v>
+        <v>3.4454</v>
       </c>
       <c r="D12" t="n">
-        <v>1.9151</v>
+        <v>1.9605</v>
       </c>
       <c r="E12" t="n">
-        <v>5.5782</v>
+        <v>5.7632</v>
       </c>
       <c r="F12" t="n">
         <v>3.9048</v>
@@ -1002,16 +1002,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4.8897</v>
+        <v>5.037</v>
       </c>
       <c r="C13" t="n">
-        <v>2.9232</v>
+        <v>3.0113</v>
       </c>
       <c r="D13" t="n">
-        <v>1.6017</v>
+        <v>1.6361</v>
       </c>
       <c r="E13" t="n">
-        <v>4.8897</v>
+        <v>5.037</v>
       </c>
       <c r="F13" t="n">
         <v>2.6372</v>
@@ -1048,16 +1048,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4.1009</v>
+        <v>4.289</v>
       </c>
       <c r="C14" t="n">
-        <v>2.4516</v>
+        <v>2.5641</v>
       </c>
       <c r="D14" t="n">
-        <v>1.2426</v>
+        <v>1.302</v>
       </c>
       <c r="E14" t="n">
-        <v>4.1009</v>
+        <v>4.289</v>
       </c>
       <c r="F14" t="n">
         <v>4.1009</v>
@@ -1090,139 +1090,139 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ropz</t>
+          <t>luchov</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.0683</v>
+        <v>4.2775</v>
       </c>
       <c r="C15" t="n">
-        <v>2.4321</v>
+        <v>2.5572</v>
       </c>
       <c r="D15" t="n">
-        <v>1.2278</v>
+        <v>1.2968</v>
       </c>
       <c r="E15" t="n">
-        <v>4.0683</v>
+        <v>4.2775</v>
       </c>
       <c r="F15" t="n">
-        <v>3.1257</v>
+        <v>3.824</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9426</v>
+        <v>0.1761</v>
       </c>
       <c r="H15" t="n">
-        <v>4.1163</v>
+        <v>5.6446</v>
       </c>
       <c r="I15" t="n">
-        <v>4.2224</v>
+        <v>5.7901</v>
       </c>
       <c r="J15" t="n">
-        <v>0.9426</v>
+        <v>0.1761</v>
       </c>
       <c r="K15" t="n">
-        <v>221</v>
+        <v>281</v>
       </c>
       <c r="L15" t="n">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="M15" t="n">
-        <v>5.165</v>
+        <v>5.9662</v>
       </c>
       <c r="N15" t="n">
-        <v>293</v>
+        <v>343</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>luchov</t>
+          <t>ropz</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4.0001</v>
+        <v>4.1362</v>
       </c>
       <c r="C16" t="n">
-        <v>2.3914</v>
+        <v>2.4727</v>
       </c>
       <c r="D16" t="n">
-        <v>1.1967</v>
+        <v>1.2337</v>
       </c>
       <c r="E16" t="n">
-        <v>4.0001</v>
+        <v>4.1362</v>
       </c>
       <c r="F16" t="n">
-        <v>3.824</v>
+        <v>3.1257</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1761</v>
+        <v>0.9426</v>
       </c>
       <c r="H16" t="n">
-        <v>5.6446</v>
+        <v>4.1163</v>
       </c>
       <c r="I16" t="n">
-        <v>5.7901</v>
+        <v>4.2224</v>
       </c>
       <c r="J16" t="n">
-        <v>0.1761</v>
+        <v>0.9426</v>
       </c>
       <c r="K16" t="n">
-        <v>281</v>
+        <v>221</v>
       </c>
       <c r="L16" t="n">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="M16" t="n">
-        <v>5.9662</v>
+        <v>5.165</v>
       </c>
       <c r="N16" t="n">
-        <v>343</v>
+        <v>293</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>XANTARES</t>
+          <t>Magnojez</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3.3518</v>
+        <v>3.4784</v>
       </c>
       <c r="C17" t="n">
-        <v>2.0038</v>
+        <v>2.0795</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9016</v>
+        <v>0.9399</v>
       </c>
       <c r="E17" t="n">
-        <v>3.3518</v>
+        <v>3.4784</v>
       </c>
       <c r="F17" t="n">
-        <v>1.9386</v>
+        <v>3.2025</v>
       </c>
       <c r="G17" t="n">
-        <v>1.4132</v>
+        <v>0.099</v>
       </c>
       <c r="H17" t="n">
-        <v>1.9386</v>
+        <v>4.2843</v>
       </c>
       <c r="I17" t="n">
-        <v>1.9886</v>
+        <v>4.2843</v>
       </c>
       <c r="J17" t="n">
-        <v>1.4132</v>
+        <v>0.099</v>
       </c>
       <c r="K17" t="n">
-        <v>173</v>
+        <v>237</v>
       </c>
       <c r="L17" t="n">
-        <v>80</v>
+        <v>41</v>
       </c>
       <c r="M17" t="n">
-        <v>3.4018</v>
+        <v>4.3833</v>
       </c>
       <c r="N17" t="n">
-        <v>253</v>
+        <v>278</v>
       </c>
     </row>
     <row r="18">
@@ -1232,16 +1232,16 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3.3264</v>
+        <v>3.4132</v>
       </c>
       <c r="C18" t="n">
-        <v>1.9886</v>
+        <v>2.0405</v>
       </c>
       <c r="D18" t="n">
-        <v>0.89</v>
+        <v>0.9108000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>3.3264</v>
+        <v>3.4132</v>
       </c>
       <c r="F18" t="n">
         <v>3.3264</v>
@@ -1274,93 +1274,93 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Magnojez</t>
+          <t>XANTARES</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.3015</v>
+        <v>3.3747</v>
       </c>
       <c r="C19" t="n">
-        <v>1.9737</v>
+        <v>2.0175</v>
       </c>
       <c r="D19" t="n">
-        <v>0.8787</v>
+        <v>0.8935999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>3.3015</v>
+        <v>3.3747</v>
       </c>
       <c r="F19" t="n">
-        <v>3.2025</v>
+        <v>1.9386</v>
       </c>
       <c r="G19" t="n">
-        <v>0.099</v>
+        <v>1.4132</v>
       </c>
       <c r="H19" t="n">
-        <v>4.2843</v>
+        <v>1.9386</v>
       </c>
       <c r="I19" t="n">
-        <v>4.2843</v>
+        <v>1.9886</v>
       </c>
       <c r="J19" t="n">
-        <v>0.099</v>
+        <v>1.4132</v>
       </c>
       <c r="K19" t="n">
-        <v>237</v>
+        <v>173</v>
       </c>
       <c r="L19" t="n">
-        <v>41</v>
+        <v>80</v>
       </c>
       <c r="M19" t="n">
-        <v>4.3833</v>
+        <v>3.4018</v>
       </c>
       <c r="N19" t="n">
-        <v>278</v>
+        <v>253</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>woxic</t>
+          <t>afro</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.9621</v>
+        <v>3.0849</v>
       </c>
       <c r="C20" t="n">
-        <v>1.7708</v>
+        <v>1.8442</v>
       </c>
       <c r="D20" t="n">
-        <v>0.7242</v>
+        <v>0.7641</v>
       </c>
       <c r="E20" t="n">
-        <v>2.9621</v>
+        <v>3.0849</v>
       </c>
       <c r="F20" t="n">
-        <v>1.6332</v>
+        <v>2.8314</v>
       </c>
       <c r="G20" t="n">
-        <v>1.3289</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.6332</v>
+        <v>3.4722</v>
       </c>
       <c r="I20" t="n">
-        <v>1.6753</v>
+        <v>3.4722</v>
       </c>
       <c r="J20" t="n">
-        <v>1.3289</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>173</v>
+        <v>238</v>
       </c>
       <c r="L20" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.0042</v>
+        <v>3.4722</v>
       </c>
       <c r="N20" t="n">
-        <v>253</v>
+        <v>238</v>
       </c>
     </row>
     <row r="21">
@@ -1370,16 +1370,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.9568</v>
+        <v>3.0648</v>
       </c>
       <c r="C21" t="n">
-        <v>1.7677</v>
+        <v>1.8322</v>
       </c>
       <c r="D21" t="n">
-        <v>0.7218</v>
+        <v>0.7552</v>
       </c>
       <c r="E21" t="n">
-        <v>2.9568</v>
+        <v>3.0648</v>
       </c>
       <c r="F21" t="n">
         <v>2.4801</v>
@@ -1412,47 +1412,47 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>afro</t>
+          <t>woxic</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.8314</v>
+        <v>3.0064</v>
       </c>
       <c r="C22" t="n">
-        <v>1.6927</v>
+        <v>1.7973</v>
       </c>
       <c r="D22" t="n">
-        <v>0.6647</v>
+        <v>0.7291</v>
       </c>
       <c r="E22" t="n">
-        <v>2.8314</v>
+        <v>3.0064</v>
       </c>
       <c r="F22" t="n">
-        <v>2.8314</v>
+        <v>1.6332</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>1.3289</v>
       </c>
       <c r="H22" t="n">
-        <v>3.4722</v>
+        <v>1.6332</v>
       </c>
       <c r="I22" t="n">
-        <v>3.4722</v>
+        <v>1.6753</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1.3289</v>
       </c>
       <c r="K22" t="n">
-        <v>238</v>
+        <v>173</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="M22" t="n">
-        <v>3.4722</v>
+        <v>3.0042</v>
       </c>
       <c r="N22" t="n">
-        <v>238</v>
+        <v>253</v>
       </c>
     </row>
     <row r="23">
@@ -1462,16 +1462,16 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.7369</v>
+        <v>2.7699</v>
       </c>
       <c r="C23" t="n">
-        <v>1.6362</v>
+        <v>1.6559</v>
       </c>
       <c r="D23" t="n">
-        <v>0.6217</v>
+        <v>0.6234</v>
       </c>
       <c r="E23" t="n">
-        <v>2.7369</v>
+        <v>2.7699</v>
       </c>
       <c r="F23" t="n">
         <v>2.8269</v>
@@ -1504,354 +1504,354 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>TeSeS</t>
+          <t>910</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.6977</v>
+        <v>2.76</v>
       </c>
       <c r="C24" t="n">
-        <v>1.6128</v>
+        <v>1.65</v>
       </c>
       <c r="D24" t="n">
-        <v>0.6038</v>
+        <v>0.619</v>
       </c>
       <c r="E24" t="n">
-        <v>2.6977</v>
+        <v>2.76</v>
       </c>
       <c r="F24" t="n">
-        <v>2.9689</v>
+        <v>2.6284</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.2712</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>3.7731</v>
+        <v>3.0278</v>
       </c>
       <c r="I24" t="n">
-        <v>3.7731</v>
+        <v>3.0278</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.2712</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>260</v>
+        <v>290</v>
       </c>
       <c r="L24" t="n">
-        <v>214</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.5019</v>
+        <v>3.0278</v>
       </c>
       <c r="N24" t="n">
-        <v>474</v>
+        <v>290</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>HUASOPEEK</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.6284</v>
+        <v>2.7158</v>
       </c>
       <c r="C25" t="n">
-        <v>1.5713</v>
+        <v>1.6236</v>
       </c>
       <c r="D25" t="n">
-        <v>0.5723</v>
+        <v>0.5993000000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>2.6284</v>
+        <v>2.7158</v>
       </c>
       <c r="F25" t="n">
-        <v>2.6284</v>
+        <v>2.5998</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>0.0162</v>
       </c>
       <c r="H25" t="n">
-        <v>3.0278</v>
+        <v>2.9653</v>
       </c>
       <c r="I25" t="n">
-        <v>3.0278</v>
+        <v>3.0417</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>0.0162</v>
       </c>
       <c r="K25" t="n">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="M25" t="n">
-        <v>3.0278</v>
+        <v>3.0579</v>
       </c>
       <c r="N25" t="n">
-        <v>290</v>
+        <v>343</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>HUASOPEEK</t>
+          <t>torzsi</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.616</v>
+        <v>2.7041</v>
       </c>
       <c r="C26" t="n">
-        <v>1.5639</v>
+        <v>1.6166</v>
       </c>
       <c r="D26" t="n">
-        <v>0.5667</v>
+        <v>0.594</v>
       </c>
       <c r="E26" t="n">
-        <v>2.616</v>
+        <v>2.7041</v>
       </c>
       <c r="F26" t="n">
-        <v>2.5998</v>
+        <v>2.56</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0162</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>2.9653</v>
+        <v>2.8782</v>
       </c>
       <c r="I26" t="n">
-        <v>3.0417</v>
+        <v>2.8782</v>
       </c>
       <c r="J26" t="n">
-        <v>0.0162</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>281</v>
+        <v>219</v>
       </c>
       <c r="L26" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.0579</v>
+        <v>2.8782</v>
       </c>
       <c r="N26" t="n">
-        <v>343</v>
+        <v>219</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>xertioN</t>
+          <t>w0nderful</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2.5893</v>
+        <v>2.6847</v>
       </c>
       <c r="C27" t="n">
-        <v>1.548</v>
+        <v>1.605</v>
       </c>
       <c r="D27" t="n">
-        <v>0.5545</v>
+        <v>0.5854</v>
       </c>
       <c r="E27" t="n">
-        <v>2.5893</v>
+        <v>2.6847</v>
       </c>
       <c r="F27" t="n">
-        <v>2.5893</v>
+        <v>2.5878</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>2.9422</v>
+        <v>2.9389</v>
       </c>
       <c r="I27" t="n">
-        <v>2.9422</v>
+        <v>2.9389</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>219</v>
+        <v>292</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>2.9422</v>
+        <v>2.9389</v>
       </c>
       <c r="N27" t="n">
-        <v>219</v>
+        <v>292</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>w0nderful</t>
+          <t>TeSeS</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.5878</v>
+        <v>2.6815</v>
       </c>
       <c r="C28" t="n">
-        <v>1.5471</v>
+        <v>1.6031</v>
       </c>
       <c r="D28" t="n">
-        <v>0.5538</v>
+        <v>0.5839</v>
       </c>
       <c r="E28" t="n">
-        <v>2.5878</v>
+        <v>2.6815</v>
       </c>
       <c r="F28" t="n">
-        <v>2.5878</v>
+        <v>2.9689</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>-0.2712</v>
       </c>
       <c r="H28" t="n">
-        <v>2.9389</v>
+        <v>3.7731</v>
       </c>
       <c r="I28" t="n">
-        <v>2.9389</v>
+        <v>3.7731</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>-0.2712</v>
       </c>
       <c r="K28" t="n">
-        <v>292</v>
+        <v>260</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>214</v>
       </c>
       <c r="M28" t="n">
-        <v>2.9389</v>
+        <v>3.5019</v>
       </c>
       <c r="N28" t="n">
-        <v>292</v>
+        <v>474</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>bLitz</t>
+          <t>latto</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2.5699</v>
+        <v>2.6198</v>
       </c>
       <c r="C29" t="n">
-        <v>1.5364</v>
+        <v>1.5662</v>
       </c>
       <c r="D29" t="n">
-        <v>0.5457</v>
+        <v>0.5564</v>
       </c>
       <c r="E29" t="n">
-        <v>2.5699</v>
+        <v>2.6198</v>
       </c>
       <c r="F29" t="n">
-        <v>2.5699</v>
+        <v>2.3918</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>2.8997</v>
+        <v>2.51</v>
       </c>
       <c r="I29" t="n">
-        <v>2.8997</v>
+        <v>2.51</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>290</v>
+        <v>171</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>2.8997</v>
+        <v>2.51</v>
       </c>
       <c r="N29" t="n">
-        <v>290</v>
+        <v>171</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>torzsi</t>
+          <t>cobrazera</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2.56</v>
+        <v>2.5999</v>
       </c>
       <c r="C30" t="n">
-        <v>1.5304</v>
+        <v>1.5543</v>
       </c>
       <c r="D30" t="n">
-        <v>0.5412</v>
+        <v>0.5475</v>
       </c>
       <c r="E30" t="n">
-        <v>2.56</v>
+        <v>2.5999</v>
       </c>
       <c r="F30" t="n">
-        <v>2.56</v>
+        <v>2.5274</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>2.8782</v>
+        <v>2.8067</v>
       </c>
       <c r="I30" t="n">
-        <v>2.8782</v>
+        <v>2.8067</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>219</v>
+        <v>290</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>2.8782</v>
+        <v>2.8067</v>
       </c>
       <c r="N30" t="n">
-        <v>219</v>
+        <v>290</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>cobrazera</t>
+          <t>bLitz</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2.5274</v>
+        <v>2.5754</v>
       </c>
       <c r="C31" t="n">
-        <v>1.5109</v>
+        <v>1.5396</v>
       </c>
       <c r="D31" t="n">
-        <v>0.5263</v>
+        <v>0.5366</v>
       </c>
       <c r="E31" t="n">
-        <v>2.5274</v>
+        <v>2.5754</v>
       </c>
       <c r="F31" t="n">
-        <v>2.5274</v>
+        <v>2.5699</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>2.8067</v>
+        <v>2.8997</v>
       </c>
       <c r="I31" t="n">
-        <v>2.8067</v>
+        <v>2.8997</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>2.8067</v>
+        <v>2.8997</v>
       </c>
       <c r="N31" t="n">
         <v>290</v>
@@ -1872,93 +1872,93 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>soulfly</t>
+          <t>xertioN</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2.4687</v>
+        <v>2.5406</v>
       </c>
       <c r="C32" t="n">
-        <v>1.4759</v>
+        <v>1.5188</v>
       </c>
       <c r="D32" t="n">
-        <v>0.4996</v>
+        <v>0.521</v>
       </c>
       <c r="E32" t="n">
-        <v>2.4687</v>
+        <v>2.5406</v>
       </c>
       <c r="F32" t="n">
-        <v>3.1231</v>
+        <v>2.5893</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.6544</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>4.1105</v>
+        <v>2.9422</v>
       </c>
       <c r="I32" t="n">
-        <v>4.2164</v>
+        <v>2.9422</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.6544</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>173</v>
+        <v>219</v>
       </c>
       <c r="L32" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.562</v>
+        <v>2.9422</v>
       </c>
       <c r="N32" t="n">
-        <v>253</v>
+        <v>219</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>latto</t>
+          <t>soulfly</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2.3918</v>
+        <v>2.5087</v>
       </c>
       <c r="C33" t="n">
-        <v>1.4299</v>
+        <v>1.4998</v>
       </c>
       <c r="D33" t="n">
-        <v>0.4646</v>
+        <v>0.5068</v>
       </c>
       <c r="E33" t="n">
-        <v>2.3918</v>
+        <v>2.5087</v>
       </c>
       <c r="F33" t="n">
-        <v>2.3918</v>
+        <v>3.1231</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>-0.6544</v>
       </c>
       <c r="H33" t="n">
-        <v>2.51</v>
+        <v>4.1105</v>
       </c>
       <c r="I33" t="n">
-        <v>2.51</v>
+        <v>4.2164</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>-0.6544</v>
       </c>
       <c r="K33" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="M33" t="n">
-        <v>2.51</v>
+        <v>3.562</v>
       </c>
       <c r="N33" t="n">
-        <v>171</v>
+        <v>253</v>
       </c>
     </row>
     <row r="34">
@@ -1968,16 +1968,16 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2.3308</v>
+        <v>2.3473</v>
       </c>
       <c r="C34" t="n">
-        <v>1.3934</v>
+        <v>1.4033</v>
       </c>
       <c r="D34" t="n">
-        <v>0.4368</v>
+        <v>0.4347</v>
       </c>
       <c r="E34" t="n">
-        <v>2.3308</v>
+        <v>2.3473</v>
       </c>
       <c r="F34" t="n">
         <v>2.2938</v>
@@ -2010,93 +2010,93 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>zont1x</t>
+          <t>dumau</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2.1662</v>
+        <v>2.169</v>
       </c>
       <c r="C35" t="n">
-        <v>1.295</v>
+        <v>1.2967</v>
       </c>
       <c r="D35" t="n">
-        <v>0.3619</v>
+        <v>0.355</v>
       </c>
       <c r="E35" t="n">
-        <v>2.1662</v>
+        <v>2.169</v>
       </c>
       <c r="F35" t="n">
-        <v>2.3361</v>
+        <v>1.9505</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.1699</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>2.388</v>
+        <v>1.9505</v>
       </c>
       <c r="I35" t="n">
-        <v>2.388</v>
+        <v>1.9505</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.1699</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="L35" t="n">
-        <v>178</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>2.2181</v>
+        <v>1.9505</v>
       </c>
       <c r="N35" t="n">
-        <v>357</v>
+        <v>171</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Brollan</t>
+          <t>iM</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2.0801</v>
+        <v>2.1096</v>
       </c>
       <c r="C36" t="n">
-        <v>1.2435</v>
+        <v>1.2612</v>
       </c>
       <c r="D36" t="n">
-        <v>0.3227</v>
+        <v>0.3285</v>
       </c>
       <c r="E36" t="n">
-        <v>2.0801</v>
+        <v>2.1096</v>
       </c>
       <c r="F36" t="n">
-        <v>2.0801</v>
+        <v>1.9938</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>2.0801</v>
+        <v>1.9938</v>
       </c>
       <c r="I36" t="n">
-        <v>2.0801</v>
+        <v>1.9938</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>219</v>
+        <v>292</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>2.0801</v>
+        <v>1.9938</v>
       </c>
       <c r="N36" t="n">
-        <v>219</v>
+        <v>292</v>
       </c>
     </row>
     <row r="37">
@@ -2106,16 +2106,16 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2.029</v>
+        <v>2.0262</v>
       </c>
       <c r="C37" t="n">
-        <v>1.213</v>
+        <v>1.2113</v>
       </c>
       <c r="D37" t="n">
-        <v>0.2994</v>
+        <v>0.2912</v>
       </c>
       <c r="E37" t="n">
-        <v>2.029</v>
+        <v>2.0262</v>
       </c>
       <c r="F37" t="n">
         <v>2.3536</v>
@@ -2148,139 +2148,139 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>iM</t>
+          <t>Brollan</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1.9938</v>
+        <v>1.9388</v>
       </c>
       <c r="C38" t="n">
-        <v>1.1919</v>
+        <v>1.1591</v>
       </c>
       <c r="D38" t="n">
-        <v>0.2834</v>
+        <v>0.2522</v>
       </c>
       <c r="E38" t="n">
-        <v>1.9938</v>
+        <v>1.9388</v>
       </c>
       <c r="F38" t="n">
-        <v>1.9938</v>
+        <v>2.0801</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>1.9938</v>
+        <v>2.0801</v>
       </c>
       <c r="I38" t="n">
-        <v>1.9938</v>
+        <v>2.0801</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>292</v>
+        <v>219</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>1.9938</v>
+        <v>2.0801</v>
       </c>
       <c r="N38" t="n">
-        <v>292</v>
+        <v>219</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>mzinho</t>
+          <t>zont1x</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1.9523</v>
+        <v>1.9387</v>
       </c>
       <c r="C39" t="n">
-        <v>1.1671</v>
+        <v>1.159</v>
       </c>
       <c r="D39" t="n">
-        <v>0.2645</v>
+        <v>0.2522</v>
       </c>
       <c r="E39" t="n">
-        <v>1.9523</v>
+        <v>1.9387</v>
       </c>
       <c r="F39" t="n">
-        <v>1.9523</v>
+        <v>2.3361</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>-0.1699</v>
       </c>
       <c r="H39" t="n">
-        <v>1.9523</v>
+        <v>2.388</v>
       </c>
       <c r="I39" t="n">
-        <v>1.9523</v>
+        <v>2.388</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>-0.1699</v>
       </c>
       <c r="K39" t="n">
-        <v>290</v>
+        <v>179</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>178</v>
       </c>
       <c r="M39" t="n">
-        <v>1.9523</v>
+        <v>2.2181</v>
       </c>
       <c r="N39" t="n">
-        <v>290</v>
+        <v>357</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>dumau</t>
+          <t>mzinho</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1.9505</v>
+        <v>1.9328</v>
       </c>
       <c r="C40" t="n">
-        <v>1.1661</v>
+        <v>1.1555</v>
       </c>
       <c r="D40" t="n">
-        <v>0.2637</v>
+        <v>0.2495</v>
       </c>
       <c r="E40" t="n">
-        <v>1.9505</v>
+        <v>1.9328</v>
       </c>
       <c r="F40" t="n">
-        <v>1.9505</v>
+        <v>1.9523</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>1.9505</v>
+        <v>1.9523</v>
       </c>
       <c r="I40" t="n">
-        <v>1.9505</v>
+        <v>1.9523</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>171</v>
+        <v>290</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>1.9505</v>
+        <v>1.9523</v>
       </c>
       <c r="N40" t="n">
-        <v>171</v>
+        <v>290</v>
       </c>
     </row>
     <row r="41">
@@ -2290,16 +2290,16 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1.88</v>
+        <v>1.8836</v>
       </c>
       <c r="C41" t="n">
-        <v>1.1239</v>
+        <v>1.1261</v>
       </c>
       <c r="D41" t="n">
-        <v>0.2316</v>
+        <v>0.2275</v>
       </c>
       <c r="E41" t="n">
-        <v>1.88</v>
+        <v>1.8836</v>
       </c>
       <c r="F41" t="n">
         <v>1.88</v>
@@ -2336,16 +2336,16 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1.7745</v>
+        <v>1.7434</v>
       </c>
       <c r="C42" t="n">
-        <v>1.0608</v>
+        <v>1.0423</v>
       </c>
       <c r="D42" t="n">
-        <v>0.1836</v>
+        <v>0.1649</v>
       </c>
       <c r="E42" t="n">
-        <v>1.7745</v>
+        <v>1.7434</v>
       </c>
       <c r="F42" t="n">
         <v>0.9792</v>
@@ -2382,16 +2382,16 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1.6647</v>
+        <v>1.6064</v>
       </c>
       <c r="C43" t="n">
-        <v>0.9952</v>
+        <v>0.9603</v>
       </c>
       <c r="D43" t="n">
-        <v>0.1336</v>
+        <v>0.1037</v>
       </c>
       <c r="E43" t="n">
-        <v>1.6647</v>
+        <v>1.6064</v>
       </c>
       <c r="F43" t="n">
         <v>1.3942</v>
@@ -2428,16 +2428,16 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1.536</v>
+        <v>1.5714</v>
       </c>
       <c r="C44" t="n">
-        <v>0.9183</v>
+        <v>0.9394</v>
       </c>
       <c r="D44" t="n">
-        <v>0.075</v>
+        <v>0.0881</v>
       </c>
       <c r="E44" t="n">
-        <v>1.536</v>
+        <v>1.5714</v>
       </c>
       <c r="F44" t="n">
         <v>1.1349</v>
@@ -2474,16 +2474,16 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1.4773</v>
+        <v>1.4875</v>
       </c>
       <c r="C45" t="n">
-        <v>0.8832</v>
+        <v>0.8893</v>
       </c>
       <c r="D45" t="n">
-        <v>0.0483</v>
+        <v>0.0506</v>
       </c>
       <c r="E45" t="n">
-        <v>1.4773</v>
+        <v>1.4875</v>
       </c>
       <c r="F45" t="n">
         <v>1.4773</v>
@@ -2516,691 +2516,691 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>MATYS</t>
+          <t>xiELO</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1.2964</v>
+        <v>1.3256</v>
       </c>
       <c r="C46" t="n">
-        <v>0.775</v>
+        <v>0.7925</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.0341</v>
+        <v>-0.0217</v>
       </c>
       <c r="E46" t="n">
-        <v>1.2964</v>
+        <v>1.3256</v>
       </c>
       <c r="F46" t="n">
-        <v>0.4435</v>
+        <v>0.9992</v>
       </c>
       <c r="G46" t="n">
-        <v>0.8529</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0.4435</v>
+        <v>0.9992</v>
       </c>
       <c r="I46" t="n">
-        <v>0.4549</v>
+        <v>0.9992</v>
       </c>
       <c r="J46" t="n">
-        <v>0.8529</v>
+        <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>287</v>
+        <v>174</v>
       </c>
       <c r="L46" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>1.3078</v>
+        <v>0.9992</v>
       </c>
       <c r="N46" t="n">
-        <v>386</v>
+        <v>174</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>dem0n</t>
+          <t>MATYS</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1.0974</v>
+        <v>1.2306</v>
       </c>
       <c r="C47" t="n">
-        <v>0.6561</v>
+        <v>0.7357</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.1246</v>
+        <v>-0.0641</v>
       </c>
       <c r="E47" t="n">
-        <v>1.0974</v>
+        <v>1.2306</v>
       </c>
       <c r="F47" t="n">
-        <v>1.0974</v>
+        <v>0.4435</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>0.8529</v>
       </c>
       <c r="H47" t="n">
-        <v>1.0974</v>
+        <v>0.4435</v>
       </c>
       <c r="I47" t="n">
-        <v>1.0974</v>
+        <v>0.4549</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>0.8529</v>
       </c>
       <c r="K47" t="n">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="M47" t="n">
-        <v>1.0974</v>
+        <v>1.3078</v>
       </c>
       <c r="N47" t="n">
-        <v>289</v>
+        <v>386</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>makazze</t>
+          <t>npl</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1.0806</v>
+        <v>1.1582</v>
       </c>
       <c r="C48" t="n">
-        <v>0.646</v>
+        <v>0.6924</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.1323</v>
+        <v>-0.0965</v>
       </c>
       <c r="E48" t="n">
-        <v>1.0806</v>
+        <v>1.1582</v>
       </c>
       <c r="F48" t="n">
-        <v>1.0806</v>
+        <v>0.9009</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>1.0806</v>
+        <v>0.9009</v>
       </c>
       <c r="I48" t="n">
-        <v>1.0806</v>
+        <v>0.9009</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>292</v>
+        <v>155</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>1.0806</v>
+        <v>0.9009</v>
       </c>
       <c r="N48" t="n">
-        <v>292</v>
+        <v>155</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>FL4MUS</t>
+          <t>dem0n</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1.0733</v>
+        <v>1.154</v>
       </c>
       <c r="C49" t="n">
-        <v>0.6415999999999999</v>
+        <v>0.6899</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.1356</v>
+        <v>-0.0984</v>
       </c>
       <c r="E49" t="n">
-        <v>1.0733</v>
+        <v>1.154</v>
       </c>
       <c r="F49" t="n">
-        <v>1.7763</v>
+        <v>1.0974</v>
       </c>
       <c r="G49" t="n">
-        <v>-0.703</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>1.7763</v>
+        <v>1.0974</v>
       </c>
       <c r="I49" t="n">
-        <v>1.7763</v>
+        <v>1.0974</v>
       </c>
       <c r="J49" t="n">
-        <v>-0.703</v>
+        <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>237</v>
+        <v>289</v>
       </c>
       <c r="L49" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>1.0733</v>
+        <v>1.0974</v>
       </c>
       <c r="N49" t="n">
-        <v>278</v>
+        <v>289</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>xiELO</t>
+          <t>FL4MUS</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.9992</v>
+        <v>1.0925</v>
       </c>
       <c r="C50" t="n">
-        <v>0.5973000000000001</v>
+        <v>0.6531</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.1693</v>
+        <v>-0.1258</v>
       </c>
       <c r="E50" t="n">
-        <v>0.9992</v>
+        <v>1.0925</v>
       </c>
       <c r="F50" t="n">
-        <v>0.9992</v>
+        <v>1.7763</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>-0.703</v>
       </c>
       <c r="H50" t="n">
-        <v>0.9992</v>
+        <v>1.7763</v>
       </c>
       <c r="I50" t="n">
-        <v>0.9992</v>
+        <v>1.7763</v>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
+        <v>-0.703</v>
       </c>
       <c r="K50" t="n">
-        <v>174</v>
+        <v>237</v>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="M50" t="n">
-        <v>0.9992</v>
+        <v>1.0733</v>
       </c>
       <c r="N50" t="n">
-        <v>174</v>
+        <v>278</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>npl</t>
+          <t>makazze</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.9009</v>
+        <v>1.0674</v>
       </c>
       <c r="C51" t="n">
-        <v>0.5386</v>
+        <v>0.6381</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.2141</v>
+        <v>-0.137</v>
       </c>
       <c r="E51" t="n">
-        <v>0.9009</v>
+        <v>1.0674</v>
       </c>
       <c r="F51" t="n">
-        <v>0.9009</v>
+        <v>1.0806</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>0.9009</v>
+        <v>1.0806</v>
       </c>
       <c r="I51" t="n">
-        <v>0.9009</v>
+        <v>1.0806</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>155</v>
+        <v>292</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>0.9009</v>
+        <v>1.0806</v>
       </c>
       <c r="N51" t="n">
-        <v>155</v>
+        <v>292</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>zorte</t>
+          <t>Rainwaker</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.7559</v>
+        <v>0.6529</v>
       </c>
       <c r="C52" t="n">
-        <v>0.4519</v>
+        <v>0.3903</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.2801</v>
+        <v>-0.3222</v>
       </c>
       <c r="E52" t="n">
-        <v>0.7559</v>
+        <v>0.6529</v>
       </c>
       <c r="F52" t="n">
-        <v>1.3304</v>
+        <v>0.6994</v>
       </c>
       <c r="G52" t="n">
-        <v>-0.5745</v>
+        <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>1.3304</v>
+        <v>0.6994</v>
       </c>
       <c r="I52" t="n">
-        <v>1.3304</v>
+        <v>0.6994</v>
       </c>
       <c r="J52" t="n">
-        <v>-0.5745</v>
+        <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="L52" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>0.7559</v>
+        <v>0.6994</v>
       </c>
       <c r="N52" t="n">
-        <v>278</v>
+        <v>238</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Rainwaker</t>
+          <t>zorte</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.6994</v>
+        <v>0.6395999999999999</v>
       </c>
       <c r="C53" t="n">
-        <v>0.4181</v>
+        <v>0.3824</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.3058</v>
+        <v>-0.3281</v>
       </c>
       <c r="E53" t="n">
-        <v>0.6994</v>
+        <v>0.6395999999999999</v>
       </c>
       <c r="F53" t="n">
-        <v>0.6994</v>
+        <v>1.3304</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>-0.5745</v>
       </c>
       <c r="H53" t="n">
-        <v>0.6994</v>
+        <v>1.3304</v>
       </c>
       <c r="I53" t="n">
-        <v>0.6994</v>
+        <v>1.3304</v>
       </c>
       <c r="J53" t="n">
-        <v>0</v>
+        <v>-0.5745</v>
       </c>
       <c r="K53" t="n">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="M53" t="n">
-        <v>0.6994</v>
+        <v>0.7559</v>
       </c>
       <c r="N53" t="n">
-        <v>238</v>
+        <v>278</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>meyern</t>
+          <t>s1zzi</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.6096</v>
+        <v>0.6145</v>
       </c>
       <c r="C54" t="n">
-        <v>0.3644</v>
+        <v>0.3674</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.3467</v>
+        <v>-0.3393</v>
       </c>
       <c r="E54" t="n">
-        <v>0.6096</v>
+        <v>0.6145</v>
       </c>
       <c r="F54" t="n">
-        <v>0.9483</v>
+        <v>0.5225</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.3387</v>
+        <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>0.9483</v>
+        <v>0.5225</v>
       </c>
       <c r="I54" t="n">
-        <v>0.9727</v>
+        <v>0.5225</v>
       </c>
       <c r="J54" t="n">
-        <v>-0.3387</v>
+        <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>281</v>
+        <v>155</v>
       </c>
       <c r="L54" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>0.634</v>
+        <v>0.5225</v>
       </c>
       <c r="N54" t="n">
-        <v>343</v>
+        <v>155</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>s1zzi</t>
+          <t>nota</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.5225</v>
+        <v>0.5211</v>
       </c>
       <c r="C55" t="n">
-        <v>0.3124</v>
+        <v>0.3115</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.3864</v>
+        <v>-0.3811</v>
       </c>
       <c r="E55" t="n">
-        <v>0.5225</v>
+        <v>0.5211</v>
       </c>
       <c r="F55" t="n">
-        <v>0.5225</v>
+        <v>0.4577</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>0.5225</v>
+        <v>0.4577</v>
       </c>
       <c r="I55" t="n">
-        <v>0.5225</v>
+        <v>0.4577</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>155</v>
+        <v>174</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>0.5225</v>
+        <v>0.4577</v>
       </c>
       <c r="N55" t="n">
-        <v>155</v>
+        <v>174</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AZUWU</t>
+          <t>meyern</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.5114</v>
+        <v>0.5139</v>
       </c>
       <c r="C56" t="n">
-        <v>0.3057</v>
+        <v>0.3072</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.3914</v>
+        <v>-0.3843</v>
       </c>
       <c r="E56" t="n">
-        <v>0.5114</v>
+        <v>0.5139</v>
       </c>
       <c r="F56" t="n">
-        <v>0.5114</v>
+        <v>0.9483</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>-0.3387</v>
       </c>
       <c r="H56" t="n">
-        <v>0.5114</v>
+        <v>0.9483</v>
       </c>
       <c r="I56" t="n">
-        <v>0.5114</v>
+        <v>0.9727</v>
       </c>
       <c r="J56" t="n">
-        <v>0</v>
+        <v>-0.3387</v>
       </c>
       <c r="K56" t="n">
-        <v>238</v>
+        <v>281</v>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="M56" t="n">
-        <v>0.5114</v>
+        <v>0.634</v>
       </c>
       <c r="N56" t="n">
-        <v>238</v>
+        <v>343</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>nota</t>
+          <t>AZUWU</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.4577</v>
+        <v>0.4168</v>
       </c>
       <c r="C57" t="n">
-        <v>0.2736</v>
+        <v>0.2492</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.4158</v>
+        <v>-0.4276</v>
       </c>
       <c r="E57" t="n">
-        <v>0.4577</v>
+        <v>0.4168</v>
       </c>
       <c r="F57" t="n">
-        <v>0.4577</v>
+        <v>0.5114</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>0.4577</v>
+        <v>0.5114</v>
       </c>
       <c r="I57" t="n">
-        <v>0.4577</v>
+        <v>0.5114</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>174</v>
+        <v>238</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>0.4577</v>
+        <v>0.5114</v>
       </c>
       <c r="N57" t="n">
-        <v>174</v>
+        <v>238</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>tN1R</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.4057</v>
+        <v>0.3283</v>
       </c>
       <c r="C58" t="n">
-        <v>0.2425</v>
+        <v>0.1963</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.4395</v>
+        <v>-0.4672</v>
       </c>
       <c r="E58" t="n">
-        <v>0.4057</v>
+        <v>0.3283</v>
       </c>
       <c r="F58" t="n">
-        <v>0.3839</v>
+        <v>0.3659</v>
       </c>
       <c r="G58" t="n">
-        <v>0.0218</v>
+        <v>0.0017</v>
       </c>
       <c r="H58" t="n">
-        <v>0.3839</v>
+        <v>0.3659</v>
       </c>
       <c r="I58" t="n">
-        <v>0.3839</v>
+        <v>0.3753</v>
       </c>
       <c r="J58" t="n">
-        <v>0.0218</v>
+        <v>0.0017</v>
       </c>
       <c r="K58" t="n">
-        <v>179</v>
+        <v>221</v>
       </c>
       <c r="L58" t="n">
-        <v>178</v>
+        <v>72</v>
       </c>
       <c r="M58" t="n">
-        <v>0.4057</v>
+        <v>0.377</v>
       </c>
       <c r="N58" t="n">
-        <v>357</v>
+        <v>293</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>Krabeni</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.3676</v>
+        <v>0.2915</v>
       </c>
       <c r="C59" t="n">
-        <v>0.2198</v>
+        <v>0.1743</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.4569</v>
+        <v>-0.4836</v>
       </c>
       <c r="E59" t="n">
-        <v>0.3676</v>
+        <v>0.2915</v>
       </c>
       <c r="F59" t="n">
-        <v>0.3659</v>
+        <v>0.2732</v>
       </c>
       <c r="G59" t="n">
-        <v>0.0017</v>
+        <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>0.3659</v>
+        <v>0.2732</v>
       </c>
       <c r="I59" t="n">
-        <v>0.3753</v>
+        <v>0.2732</v>
       </c>
       <c r="J59" t="n">
-        <v>0.0017</v>
+        <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>221</v>
+        <v>289</v>
       </c>
       <c r="L59" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>0.377</v>
+        <v>0.2732</v>
       </c>
       <c r="N59" t="n">
-        <v>293</v>
+        <v>289</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Krabeni</t>
+          <t>tN1R</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.2732</v>
+        <v>0.2578</v>
       </c>
       <c r="C60" t="n">
-        <v>0.1633</v>
+        <v>0.1541</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.4998</v>
+        <v>-0.4987</v>
       </c>
       <c r="E60" t="n">
-        <v>0.2732</v>
+        <v>0.2578</v>
       </c>
       <c r="F60" t="n">
-        <v>0.2732</v>
+        <v>0.3839</v>
       </c>
       <c r="G60" t="n">
-        <v>0</v>
+        <v>0.0218</v>
       </c>
       <c r="H60" t="n">
-        <v>0.2732</v>
+        <v>0.3839</v>
       </c>
       <c r="I60" t="n">
-        <v>0.2732</v>
+        <v>0.3839</v>
       </c>
       <c r="J60" t="n">
-        <v>0</v>
+        <v>0.0218</v>
       </c>
       <c r="K60" t="n">
-        <v>289</v>
+        <v>179</v>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>178</v>
       </c>
       <c r="M60" t="n">
-        <v>0.2732</v>
+        <v>0.4057</v>
       </c>
       <c r="N60" t="n">
-        <v>289</v>
+        <v>357</v>
       </c>
     </row>
     <row r="61">
@@ -3210,16 +3210,16 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.0774</v>
+        <v>-0.0361</v>
       </c>
       <c r="C61" t="n">
-        <v>0.0463</v>
+        <v>-0.0216</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.589</v>
+        <v>-0.6299</v>
       </c>
       <c r="E61" t="n">
-        <v>0.0774</v>
+        <v>-0.0361</v>
       </c>
       <c r="F61" t="n">
         <v>0.1461</v>
@@ -3252,139 +3252,139 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Jame</t>
+          <t>kensizor</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.1449</v>
+        <v>-0.1531</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.0866</v>
+        <v>-0.0915</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.6902</v>
+        <v>-0.6822</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.1449</v>
+        <v>-0.1531</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.1449</v>
+        <v>-0.2482</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.1449</v>
+        <v>-0.2482</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.1449</v>
+        <v>-0.2482</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>174</v>
+        <v>155</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>-0.1449</v>
+        <v>-0.2482</v>
       </c>
       <c r="N62" t="n">
-        <v>174</v>
+        <v>155</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>cmtry</t>
+          <t>Jame</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.1896</v>
+        <v>-0.1741</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.1133</v>
+        <v>-0.1041</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.7105</v>
+        <v>-0.6916</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.1896</v>
+        <v>-0.1741</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.1896</v>
+        <v>-0.1449</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.1896</v>
+        <v>-0.1449</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.1896</v>
+        <v>-0.1449</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>289</v>
+        <v>174</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>-0.1896</v>
+        <v>-0.1449</v>
       </c>
       <c r="N63" t="n">
-        <v>289</v>
+        <v>174</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>kensizor</t>
+          <t>cmtry</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.2482</v>
+        <v>-0.3228</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.1484</v>
+        <v>-0.193</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.7372</v>
+        <v>-0.758</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.2482</v>
+        <v>-0.3228</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.2482</v>
+        <v>-0.1896</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.2482</v>
+        <v>-0.1896</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.2482</v>
+        <v>-0.1896</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>155</v>
+        <v>289</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>-0.2482</v>
+        <v>-0.1896</v>
       </c>
       <c r="N64" t="n">
-        <v>155</v>
+        <v>289</v>
       </c>
     </row>
     <row r="65">
@@ -3394,16 +3394,16 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.2968</v>
+        <v>-0.4846</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.1774</v>
+        <v>-0.2897</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.7593</v>
+        <v>-0.8303</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.2968</v>
+        <v>-0.4846</v>
       </c>
       <c r="F65" t="n">
         <v>-0.2968</v>
@@ -3440,16 +3440,16 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.3955</v>
+        <v>-0.5702</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.2364</v>
+        <v>-0.3409</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.8042</v>
+        <v>-0.8685</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.3955</v>
+        <v>-0.5702</v>
       </c>
       <c r="F66" t="n">
         <v>-0.3955</v>
@@ -3482,93 +3482,93 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>zweih</t>
+          <t>esenthial</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.5295</v>
+        <v>-0.7619</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.3165</v>
+        <v>-0.4555</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.8652</v>
+        <v>-0.9540999999999999</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.5295</v>
+        <v>-0.7619</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.5295</v>
+        <v>-0.6452</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>-0.5295</v>
+        <v>-0.6452</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.5295</v>
+        <v>-0.6452</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>174</v>
+        <v>155</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>-0.5295</v>
+        <v>-0.6452</v>
       </c>
       <c r="N67" t="n">
-        <v>174</v>
+        <v>155</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>esenthial</t>
+          <t>zweih</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-0.6452</v>
+        <v>-0.9053</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.3857</v>
+        <v>-0.5412</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.9179</v>
+        <v>-1.0182</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.6452</v>
+        <v>-0.9053</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.6452</v>
+        <v>-0.5295</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>-0.6452</v>
+        <v>-0.5295</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.6452</v>
+        <v>-0.5295</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>155</v>
+        <v>174</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>-0.6452</v>
+        <v>-0.5295</v>
       </c>
       <c r="N68" t="n">
-        <v>155</v>
+        <v>174</v>
       </c>
     </row>
     <row r="69">
@@ -3578,16 +3578,16 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-0.8014</v>
+        <v>-0.9126</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.4791</v>
+        <v>-0.5456</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.989</v>
+        <v>-1.0215</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.8014</v>
+        <v>-0.9126</v>
       </c>
       <c r="F69" t="n">
         <v>-0.478</v>
@@ -3620,93 +3620,93 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>alex666</t>
+          <t>xelex</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-0.8537</v>
+        <v>-1.0313</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.5104</v>
+        <v>-0.6165</v>
       </c>
       <c r="D70" t="n">
-        <v>-1.0128</v>
+        <v>-1.0745</v>
       </c>
       <c r="E70" t="n">
-        <v>-0.8537</v>
+        <v>-1.0313</v>
       </c>
       <c r="F70" t="n">
-        <v>-0.8537</v>
+        <v>-0.9301</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>-0.8537</v>
+        <v>-0.9301</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.8537</v>
+        <v>-0.9301</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>155</v>
+        <v>219</v>
       </c>
       <c r="L70" t="n">
         <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>-0.8537</v>
+        <v>-0.9301</v>
       </c>
       <c r="N70" t="n">
-        <v>155</v>
+        <v>219</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>xelex</t>
+          <t>alex666</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-0.9301</v>
+        <v>-1.1385</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.556</v>
+        <v>-0.6806</v>
       </c>
       <c r="D71" t="n">
-        <v>-1.0476</v>
+        <v>-1.1224</v>
       </c>
       <c r="E71" t="n">
-        <v>-0.9301</v>
+        <v>-1.1385</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.9301</v>
+        <v>-0.8537</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>-0.9301</v>
+        <v>-0.8537</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.9301</v>
+        <v>-0.8537</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>219</v>
+        <v>155</v>
       </c>
       <c r="L71" t="n">
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>-0.9301</v>
+        <v>-0.8537</v>
       </c>
       <c r="N71" t="n">
-        <v>219</v>
+        <v>155</v>
       </c>
     </row>
     <row r="72">
@@ -3716,16 +3716,16 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-1.2485</v>
+        <v>-1.365</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.7464</v>
+        <v>-0.8159999999999999</v>
       </c>
       <c r="D72" t="n">
-        <v>-1.1925</v>
+        <v>-1.2235</v>
       </c>
       <c r="E72" t="n">
-        <v>-1.2485</v>
+        <v>-1.365</v>
       </c>
       <c r="F72" t="n">
         <v>-1.2485</v>
@@ -3762,16 +3762,16 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-1.4884</v>
+        <v>-1.8282</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.8898</v>
+        <v>-1.0929</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.3018</v>
+        <v>-1.4304</v>
       </c>
       <c r="E73" t="n">
-        <v>-1.4884</v>
+        <v>-1.8282</v>
       </c>
       <c r="F73" t="n">
         <v>-1.4884</v>
@@ -3808,16 +3808,16 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-1.5139</v>
+        <v>-1.8659</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.9051</v>
+        <v>-1.1155</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.3134</v>
+        <v>-1.4473</v>
       </c>
       <c r="E74" t="n">
-        <v>-1.5139</v>
+        <v>-1.8659</v>
       </c>
       <c r="F74" t="n">
         <v>-1.6642</v>
@@ -3850,185 +3850,185 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>saadzin</t>
+          <t>Techno</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-1.7966</v>
+        <v>-2.0771</v>
       </c>
       <c r="C75" t="n">
-        <v>-1.0741</v>
+        <v>-1.2417</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.4421</v>
+        <v>-1.5416</v>
       </c>
       <c r="E75" t="n">
-        <v>-1.7966</v>
+        <v>-2.0771</v>
       </c>
       <c r="F75" t="n">
-        <v>-1.7966</v>
+        <v>-1.8641</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>-1.7966</v>
+        <v>-1.8641</v>
       </c>
       <c r="I75" t="n">
-        <v>-1.7966</v>
+        <v>-1.8641</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>171</v>
+        <v>290</v>
       </c>
       <c r="L75" t="n">
         <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>-1.7966</v>
+        <v>-1.8641</v>
       </c>
       <c r="N75" t="n">
-        <v>171</v>
+        <v>290</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Techno</t>
+          <t>mezii</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-1.8641</v>
+        <v>-2.0838</v>
       </c>
       <c r="C76" t="n">
-        <v>-1.1144</v>
+        <v>-1.2458</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.4728</v>
+        <v>-1.5446</v>
       </c>
       <c r="E76" t="n">
-        <v>-1.8641</v>
+        <v>-2.0838</v>
       </c>
       <c r="F76" t="n">
-        <v>-1.8641</v>
+        <v>-1.5889</v>
       </c>
       <c r="G76" t="n">
-        <v>0</v>
+        <v>-0.3794</v>
       </c>
       <c r="H76" t="n">
-        <v>-1.8641</v>
+        <v>-1.5889</v>
       </c>
       <c r="I76" t="n">
-        <v>-1.8641</v>
+        <v>-1.6298</v>
       </c>
       <c r="J76" t="n">
-        <v>0</v>
+        <v>-0.3794</v>
       </c>
       <c r="K76" t="n">
-        <v>290</v>
+        <v>221</v>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="M76" t="n">
-        <v>-1.8641</v>
+        <v>-2.0092</v>
       </c>
       <c r="N76" t="n">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Aleksib</t>
+          <t>saadzin</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-1.95</v>
+        <v>-2.1593</v>
       </c>
       <c r="C77" t="n">
-        <v>-1.1658</v>
+        <v>-1.2909</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.5119</v>
+        <v>-1.5783</v>
       </c>
       <c r="E77" t="n">
-        <v>-1.95</v>
+        <v>-2.1593</v>
       </c>
       <c r="F77" t="n">
-        <v>-1.95</v>
+        <v>-1.7966</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>-1.95</v>
+        <v>-1.7966</v>
       </c>
       <c r="I77" t="n">
-        <v>-1.95</v>
+        <v>-1.7966</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>292</v>
+        <v>171</v>
       </c>
       <c r="L77" t="n">
         <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>-1.95</v>
+        <v>-1.7966</v>
       </c>
       <c r="N77" t="n">
-        <v>292</v>
+        <v>171</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>mezii</t>
+          <t>Aleksib</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-1.9683</v>
+        <v>-2.3181</v>
       </c>
       <c r="C78" t="n">
-        <v>-1.1767</v>
+        <v>-1.3858</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.5202</v>
+        <v>-1.6493</v>
       </c>
       <c r="E78" t="n">
-        <v>-1.9683</v>
+        <v>-2.3181</v>
       </c>
       <c r="F78" t="n">
-        <v>-1.5889</v>
+        <v>-1.95</v>
       </c>
       <c r="G78" t="n">
-        <v>-0.3794</v>
+        <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>-1.5889</v>
+        <v>-1.95</v>
       </c>
       <c r="I78" t="n">
-        <v>-1.6298</v>
+        <v>-1.95</v>
       </c>
       <c r="J78" t="n">
-        <v>-0.3794</v>
+        <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>221</v>
+        <v>292</v>
       </c>
       <c r="L78" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>-2.0092</v>
+        <v>-1.95</v>
       </c>
       <c r="N78" t="n">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="79">
@@ -4038,16 +4038,16 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-2.4695</v>
+        <v>-2.8546</v>
       </c>
       <c r="C79" t="n">
-        <v>-1.4763</v>
+        <v>-1.7066</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.7484</v>
+        <v>-1.8889</v>
       </c>
       <c r="E79" t="n">
-        <v>-2.4695</v>
+        <v>-2.8546</v>
       </c>
       <c r="F79" t="n">
         <v>-1.0059</v>
@@ -4084,16 +4084,16 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-3.7452</v>
+        <v>-4.2153</v>
       </c>
       <c r="C80" t="n">
-        <v>-2.239</v>
+        <v>-2.52</v>
       </c>
       <c r="D80" t="n">
-        <v>-2.3291</v>
+        <v>-2.4967</v>
       </c>
       <c r="E80" t="n">
-        <v>-3.7452</v>
+        <v>-4.2153</v>
       </c>
       <c r="F80" t="n">
         <v>-3.7452</v>
@@ -4130,16 +4130,16 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-7.5605</v>
+        <v>-8.047800000000001</v>
       </c>
       <c r="C81" t="n">
-        <v>-4.5199</v>
+        <v>-4.8112</v>
       </c>
       <c r="D81" t="n">
-        <v>-4.0659</v>
+        <v>-4.2086</v>
       </c>
       <c r="E81" t="n">
-        <v>-7.5605</v>
+        <v>-8.047800000000001</v>
       </c>
       <c r="F81" t="n">
         <v>-4.5605</v>
